--- a/01_raw_data/4.1_SOCS/raw/input/D2.7.SVY.HLTH.xlsx
+++ b/01_raw_data/4.1_SOCS/raw/input/D2.7.SVY.HLTH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28906"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/bstacy_worldbank_org/Documents/DECIS/SPI/Data/SPI 2023/01_raw_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldbankgroup-my.sharepoint.com/personal/zprinsloo_worldbank_org/Documents/spi/technical-work/SPI-Zander/SPI/01_raw_data/4.1_SOCS/raw/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="537" documentId="13_ncr:1_{11FE9B5C-999D-4F88-92BE-56D25BAF2225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00AE786D-7931-4618-A64A-7A50357038BC}"/>
+  <xr:revisionPtr revIDLastSave="557" documentId="13_ncr:1_{11FE9B5C-999D-4F88-92BE-56D25BAF2225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D58F3F9-B535-AF4D-AE9E-5FE8B70B1664}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" tabRatio="735" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2016-20 DCS" sheetId="35" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="499">
   <si>
     <t>Time</t>
   </si>
@@ -1573,12 +1573,15 @@
   <si>
     <t>ZAR</t>
   </si>
+  <si>
+    <t>YR2025</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2105,12 +2108,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0AFD623-1ABC-43BC-A0BD-2619361D9EAD}">
   <dimension ref="A1:AM192"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>0</v>
       </c>
@@ -2223,7 +2226,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:39">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -2234,7 +2237,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:39">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -2353,7 +2356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -2472,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:39">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -2591,7 +2594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -2710,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:39">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -2829,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:39">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -2948,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:39">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -3067,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:39">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -3186,7 +3189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:39">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -3305,7 +3308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:39">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -3424,7 +3427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:39">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -3543,7 +3546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:39">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -3662,7 +3665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:39">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -3781,7 +3784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:39">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -3900,7 +3903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:39">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -4019,7 +4022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:39">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>56</v>
       </c>
@@ -4138,7 +4141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:39">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>57</v>
       </c>
@@ -4257,7 +4260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:39">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -4376,7 +4379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:39">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>59</v>
       </c>
@@ -4495,7 +4498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:39">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -4614,7 +4617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:39">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -4733,7 +4736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:39">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -4852,7 +4855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:39">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -4971,7 +4974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:39">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -5090,7 +5093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:39">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -5209,7 +5212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:39">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>66</v>
       </c>
@@ -5328,7 +5331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:39">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -5447,7 +5450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:39">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -5566,7 +5569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:39">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>69</v>
       </c>
@@ -5685,7 +5688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:39">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -5804,7 +5807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:39">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>71</v>
       </c>
@@ -5923,7 +5926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:39">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -6042,7 +6045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:39">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -6161,7 +6164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:39">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -6280,7 +6283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:39">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>75</v>
       </c>
@@ -6399,7 +6402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:39">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>76</v>
       </c>
@@ -6518,7 +6521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:39">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>77</v>
       </c>
@@ -6637,7 +6640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:39">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -6756,7 +6759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:39">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -6875,7 +6878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:39">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -6994,7 +6997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:39">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -7113,7 +7116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:39">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -7232,7 +7235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:39">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>83</v>
       </c>
@@ -7351,7 +7354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:39">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -7470,7 +7473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:39">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -7589,7 +7592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:39">
+    <row r="48" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>86</v>
       </c>
@@ -7708,7 +7711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:39">
+    <row r="49" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -7827,7 +7830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:39">
+    <row r="50" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>88</v>
       </c>
@@ -7946,7 +7949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:39">
+    <row r="51" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -8065,7 +8068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:39">
+    <row r="52" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>90</v>
       </c>
@@ -8184,7 +8187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:39">
+    <row r="53" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>91</v>
       </c>
@@ -8303,7 +8306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:39">
+    <row r="54" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>92</v>
       </c>
@@ -8422,7 +8425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:39">
+    <row r="55" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>93</v>
       </c>
@@ -8541,7 +8544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:39">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>94</v>
       </c>
@@ -8660,7 +8663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:39">
+    <row r="57" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>95</v>
       </c>
@@ -8779,7 +8782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:39">
+    <row r="58" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>96</v>
       </c>
@@ -8898,7 +8901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:39">
+    <row r="59" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>97</v>
       </c>
@@ -9017,7 +9020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:39">
+    <row r="60" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>98</v>
       </c>
@@ -9136,7 +9139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:39">
+    <row r="61" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>99</v>
       </c>
@@ -9255,7 +9258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:39">
+    <row r="62" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>100</v>
       </c>
@@ -9374,7 +9377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:39">
+    <row r="63" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>101</v>
       </c>
@@ -9493,7 +9496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:39">
+    <row r="64" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>102</v>
       </c>
@@ -9612,7 +9615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:39">
+    <row r="65" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>103</v>
       </c>
@@ -9731,7 +9734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:39">
+    <row r="66" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>104</v>
       </c>
@@ -9850,7 +9853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:39">
+    <row r="67" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>105</v>
       </c>
@@ -9969,7 +9972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:39">
+    <row r="68" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>106</v>
       </c>
@@ -10088,7 +10091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:39">
+    <row r="69" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>107</v>
       </c>
@@ -10207,7 +10210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:39">
+    <row r="70" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>108</v>
       </c>
@@ -10326,7 +10329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:39">
+    <row r="71" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>109</v>
       </c>
@@ -10445,7 +10448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:39">
+    <row r="72" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>110</v>
       </c>
@@ -10564,7 +10567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:39">
+    <row r="73" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>111</v>
       </c>
@@ -10683,7 +10686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:39">
+    <row r="74" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>112</v>
       </c>
@@ -10802,7 +10805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:39">
+    <row r="75" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>113</v>
       </c>
@@ -10921,7 +10924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:39">
+    <row r="76" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>114</v>
       </c>
@@ -11040,7 +11043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:39">
+    <row r="77" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>115</v>
       </c>
@@ -11159,7 +11162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:39">
+    <row r="78" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>116</v>
       </c>
@@ -11278,7 +11281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:39">
+    <row r="79" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>117</v>
       </c>
@@ -11397,7 +11400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:39">
+    <row r="80" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>118</v>
       </c>
@@ -11516,7 +11519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:39">
+    <row r="81" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>119</v>
       </c>
@@ -11635,7 +11638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:39">
+    <row r="82" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>120</v>
       </c>
@@ -11754,7 +11757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:39">
+    <row r="83" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>121</v>
       </c>
@@ -11873,7 +11876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:39">
+    <row r="84" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>122</v>
       </c>
@@ -11992,7 +11995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:39">
+    <row r="85" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>123</v>
       </c>
@@ -12111,7 +12114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:39">
+    <row r="86" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>124</v>
       </c>
@@ -12230,7 +12233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:39">
+    <row r="87" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>125</v>
       </c>
@@ -12349,7 +12352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:39">
+    <row r="88" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>126</v>
       </c>
@@ -12468,7 +12471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:39">
+    <row r="89" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>127</v>
       </c>
@@ -12587,7 +12590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:39">
+    <row r="90" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>128</v>
       </c>
@@ -12706,7 +12709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:39">
+    <row r="91" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>129</v>
       </c>
@@ -12825,7 +12828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:39">
+    <row r="92" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>130</v>
       </c>
@@ -12944,7 +12947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:39">
+    <row r="93" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>131</v>
       </c>
@@ -13063,7 +13066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:39">
+    <row r="94" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>132</v>
       </c>
@@ -13182,7 +13185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:39">
+    <row r="95" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>133</v>
       </c>
@@ -13301,7 +13304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:39">
+    <row r="96" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>134</v>
       </c>
@@ -13420,7 +13423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:39">
+    <row r="97" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>135</v>
       </c>
@@ -13539,7 +13542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:39">
+    <row r="98" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>136</v>
       </c>
@@ -13658,7 +13661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:39">
+    <row r="99" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>137</v>
       </c>
@@ -13777,7 +13780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:39">
+    <row r="100" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>138</v>
       </c>
@@ -13896,7 +13899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:39">
+    <row r="101" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>139</v>
       </c>
@@ -14015,7 +14018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:39">
+    <row r="102" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>140</v>
       </c>
@@ -14134,7 +14137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:39">
+    <row r="103" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>141</v>
       </c>
@@ -14253,7 +14256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:39">
+    <row r="104" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>142</v>
       </c>
@@ -14372,7 +14375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:39">
+    <row r="105" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>143</v>
       </c>
@@ -14491,7 +14494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:39">
+    <row r="106" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>144</v>
       </c>
@@ -14610,7 +14613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:39">
+    <row r="107" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>145</v>
       </c>
@@ -14729,7 +14732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:39">
+    <row r="108" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>146</v>
       </c>
@@ -14848,7 +14851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:39">
+    <row r="109" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>147</v>
       </c>
@@ -14967,7 +14970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:39">
+    <row r="110" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>148</v>
       </c>
@@ -15086,7 +15089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:39">
+    <row r="111" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>149</v>
       </c>
@@ -15205,7 +15208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:39">
+    <row r="112" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>150</v>
       </c>
@@ -15324,7 +15327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:39">
+    <row r="113" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>151</v>
       </c>
@@ -15443,7 +15446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:39">
+    <row r="114" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>152</v>
       </c>
@@ -15562,7 +15565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:39">
+    <row r="115" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>153</v>
       </c>
@@ -15681,7 +15684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:39">
+    <row r="116" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>154</v>
       </c>
@@ -15800,7 +15803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:39">
+    <row r="117" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>155</v>
       </c>
@@ -15919,7 +15922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:39">
+    <row r="118" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>156</v>
       </c>
@@ -16038,7 +16041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:39">
+    <row r="119" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>157</v>
       </c>
@@ -16157,7 +16160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:39">
+    <row r="120" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>158</v>
       </c>
@@ -16276,7 +16279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:39">
+    <row r="121" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>159</v>
       </c>
@@ -16395,7 +16398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:39">
+    <row r="122" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>160</v>
       </c>
@@ -16514,7 +16517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:39">
+    <row r="123" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>161</v>
       </c>
@@ -16633,7 +16636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:39">
+    <row r="124" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>162</v>
       </c>
@@ -16752,7 +16755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:39">
+    <row r="125" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>163</v>
       </c>
@@ -16871,7 +16874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:39">
+    <row r="126" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>164</v>
       </c>
@@ -16990,7 +16993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:39">
+    <row r="127" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>165</v>
       </c>
@@ -17109,7 +17112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:39">
+    <row r="128" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>166</v>
       </c>
@@ -17228,7 +17231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:39">
+    <row r="129" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>167</v>
       </c>
@@ -17347,7 +17350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:39">
+    <row r="130" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>168</v>
       </c>
@@ -17466,7 +17469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:39">
+    <row r="131" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>169</v>
       </c>
@@ -17585,7 +17588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:39">
+    <row r="132" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>170</v>
       </c>
@@ -17704,7 +17707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:39">
+    <row r="133" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>171</v>
       </c>
@@ -17823,7 +17826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:39">
+    <row r="134" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>172</v>
       </c>
@@ -17942,7 +17945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:39">
+    <row r="135" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>173</v>
       </c>
@@ -18061,7 +18064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:39">
+    <row r="136" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>174</v>
       </c>
@@ -18180,7 +18183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:39">
+    <row r="137" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>175</v>
       </c>
@@ -18299,7 +18302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:39">
+    <row r="138" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>176</v>
       </c>
@@ -18418,7 +18421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:39">
+    <row r="139" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>177</v>
       </c>
@@ -18537,7 +18540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:39">
+    <row r="140" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>178</v>
       </c>
@@ -18656,7 +18659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:39">
+    <row r="141" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>179</v>
       </c>
@@ -18775,7 +18778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:39">
+    <row r="142" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>180</v>
       </c>
@@ -18894,7 +18897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:39">
+    <row r="143" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>181</v>
       </c>
@@ -19013,7 +19016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:39">
+    <row r="144" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>182</v>
       </c>
@@ -19132,7 +19135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:39">
+    <row r="145" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>183</v>
       </c>
@@ -19251,7 +19254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:39">
+    <row r="146" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>184</v>
       </c>
@@ -19370,7 +19373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:39">
+    <row r="147" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>185</v>
       </c>
@@ -19489,7 +19492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:39">
+    <row r="148" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>186</v>
       </c>
@@ -19608,7 +19611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:39">
+    <row r="149" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>187</v>
       </c>
@@ -19727,7 +19730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:39">
+    <row r="150" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>188</v>
       </c>
@@ -19846,7 +19849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:39">
+    <row r="151" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>189</v>
       </c>
@@ -19965,7 +19968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:39">
+    <row r="152" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>190</v>
       </c>
@@ -20084,7 +20087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:39">
+    <row r="153" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>191</v>
       </c>
@@ -20203,7 +20206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:39">
+    <row r="154" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>192</v>
       </c>
@@ -20322,7 +20325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:39">
+    <row r="155" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>193</v>
       </c>
@@ -20441,7 +20444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:39">
+    <row r="156" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>194</v>
       </c>
@@ -20560,7 +20563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:39">
+    <row r="157" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>195</v>
       </c>
@@ -20679,7 +20682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:39">
+    <row r="158" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>196</v>
       </c>
@@ -20798,7 +20801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:39">
+    <row r="159" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>197</v>
       </c>
@@ -20917,7 +20920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:39">
+    <row r="160" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>198</v>
       </c>
@@ -21036,7 +21039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:39">
+    <row r="161" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>199</v>
       </c>
@@ -21155,7 +21158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:39">
+    <row r="162" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>200</v>
       </c>
@@ -21274,7 +21277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:39">
+    <row r="163" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>201</v>
       </c>
@@ -21393,7 +21396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:39">
+    <row r="164" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>202</v>
       </c>
@@ -21512,7 +21515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:39">
+    <row r="165" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>203</v>
       </c>
@@ -21631,7 +21634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:39">
+    <row r="166" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>204</v>
       </c>
@@ -21750,7 +21753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:39">
+    <row r="167" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>205</v>
       </c>
@@ -21869,7 +21872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:39">
+    <row r="168" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>206</v>
       </c>
@@ -21988,7 +21991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:39">
+    <row r="169" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>207</v>
       </c>
@@ -22107,7 +22110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:39">
+    <row r="170" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>208</v>
       </c>
@@ -22226,7 +22229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:39">
+    <row r="171" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>209</v>
       </c>
@@ -22345,7 +22348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:39">
+    <row r="172" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>210</v>
       </c>
@@ -22464,7 +22467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:39">
+    <row r="173" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>211</v>
       </c>
@@ -22583,7 +22586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:39">
+    <row r="174" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>212</v>
       </c>
@@ -22702,7 +22705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:39">
+    <row r="175" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>213</v>
       </c>
@@ -22821,7 +22824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:39">
+    <row r="176" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>214</v>
       </c>
@@ -22940,7 +22943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:39">
+    <row r="177" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>215</v>
       </c>
@@ -23059,7 +23062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:39">
+    <row r="178" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>216</v>
       </c>
@@ -23178,7 +23181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:39">
+    <row r="179" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>217</v>
       </c>
@@ -23297,7 +23300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:39">
+    <row r="180" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>218</v>
       </c>
@@ -23416,7 +23419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:39">
+    <row r="181" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>219</v>
       </c>
@@ -23535,7 +23538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:39">
+    <row r="182" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>220</v>
       </c>
@@ -23654,7 +23657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:39">
+    <row r="183" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>221</v>
       </c>
@@ -23773,7 +23776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:39">
+    <row r="184" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>222</v>
       </c>
@@ -23892,7 +23895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:39">
+    <row r="185" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>223</v>
       </c>
@@ -24011,7 +24014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:39">
+    <row r="186" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>224</v>
       </c>
@@ -24130,7 +24133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:39">
+    <row r="187" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>225</v>
       </c>
@@ -24249,7 +24252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:39">
+    <row r="188" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>226</v>
       </c>
@@ -24368,7 +24371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:39">
+    <row r="189" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>227</v>
       </c>
@@ -24487,7 +24490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:39">
+    <row r="190" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>228</v>
       </c>
@@ -24606,7 +24609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:39">
+    <row r="191" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>229</v>
       </c>
@@ -24725,7 +24728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:39">
+    <row r="192" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>230</v>
       </c>
@@ -24847,6 +24850,9 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -24855,21 +24861,22 @@
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AX193"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AY193"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" style="3" customWidth="1"/>
-    <col min="6" max="40" width="8.85546875" style="3"/>
-    <col min="41" max="41" width="8.7109375" style="3"/>
-    <col min="42" max="45" width="9.140625" style="3"/>
-    <col min="50" max="50" width="217.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="3" hidden="1" customWidth="1"/>
+    <col min="6" max="41" width="8.83203125" style="3" hidden="1" customWidth="1"/>
+    <col min="42" max="43" width="8.83203125" style="3" customWidth="1"/>
+    <col min="44" max="45" width="9.1640625" style="3"/>
+    <col min="46" max="46" width="8.83203125" style="3"/>
+    <col min="51" max="51" width="200.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A1" s="33"/>
       <c r="B1" s="33"/>
       <c r="E1" s="8"/>
@@ -24897,7 +24904,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:50">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="11"/>
       <c r="C2" s="12">
@@ -25049,7 +25056,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:50" s="4" customFormat="1" ht="30.75">
+    <row r="3" spans="1:51" s="4" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>232</v>
       </c>
@@ -25185,8 +25192,8 @@
       <c r="AS3" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="AT3" s="27" t="s">
-        <v>240</v>
+      <c r="AT3" s="5" t="s">
+        <v>498</v>
       </c>
       <c r="AU3" s="27" t="s">
         <v>240</v>
@@ -25197,11 +25204,14 @@
       <c r="AW3" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="AX3" s="4" t="s">
+      <c r="AX3" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="AY3" s="4" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="4" spans="1:50">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>1</v>
       </c>
@@ -25327,16 +25337,17 @@
       <c r="AQ4" s="13"/>
       <c r="AR4" s="13"/>
       <c r="AS4" s="13"/>
-      <c r="AT4" s="2"/>
+      <c r="AT4" s="13"/>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
-      <c r="AX4" t="str">
-        <f>+IF($F4=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G4=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H4=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I4=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J4=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K4=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L4=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M4=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N4=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O4=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P4=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q4=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R4=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S4=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T4=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U4=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V4=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W4=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X4=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y4=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z4=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA4=1,RIGHT(AA$3,4)&amp;", ","")&amp;IF($AB4=1,RIGHT(AB$3,4)&amp;", ","")&amp;IF($AC4=1,RIGHT(AC$3,4)&amp;", ","")&amp;IF($AD4=1,RIGHT(AD$3,4)&amp;", ","")&amp;IF($AE4=1,RIGHT(AE$3,4)&amp;", ","")&amp;IF($AF4=1,RIGHT(AF$3,4)&amp;", ","")&amp;IF($AG4=1,RIGHT(AG$3,4)&amp;", ","")&amp;IF($AH4=1,RIGHT(AH$3,4)&amp;", ","")&amp;IF($AI4=1,RIGHT(AI$3,4)&amp;", ","")&amp;IF($AJ4=1,RIGHT(AJ$3,4)&amp;", ","")&amp;IF($AK4=1,RIGHT(AK$3,4)&amp;", ","")&amp;IF($AL4=1,RIGHT(AL$3,4)&amp;", ","")&amp;IF($AM4=1,RIGHT(AM$3,4)&amp;", ","")&amp;IF($AN4=1,RIGHT(AN$3,4)&amp;", ","")&amp;IF($AO4=1,RIGHT(AO$3,4)&amp;", ","")&amp;IF($AP4=1,RIGHT(AP$3,4)&amp;", ","")&amp;IF($AQ4=1,RIGHT(AQ$3,4)&amp;", ","")&amp;IF($AR4=1,RIGHT(AR$3,4)&amp;", ","")&amp;IF($AS4=1,RIGHT(AS$3,4)&amp;", ","")</f>
+      <c r="AX4" s="2"/>
+      <c r="AY4" t="str">
+        <f>+IF($F4=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G4=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H4=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I4=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J4=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K4=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L4=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M4=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N4=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O4=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P4=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q4=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R4=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S4=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T4=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U4=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V4=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W4=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X4=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y4=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z4=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA4=1,RIGHT(AA$3,4)&amp;", ","")&amp;IF($AB4=1,RIGHT(AB$3,4)&amp;", ","")&amp;IF($AC4=1,RIGHT(AC$3,4)&amp;", ","")&amp;IF($AD4=1,RIGHT(AD$3,4)&amp;", ","")&amp;IF($AE4=1,RIGHT(AE$3,4)&amp;", ","")&amp;IF($AF4=1,RIGHT(AF$3,4)&amp;", ","")&amp;IF($AG4=1,RIGHT(AG$3,4)&amp;", ","")&amp;IF($AH4=1,RIGHT(AH$3,4)&amp;", ","")&amp;IF($AI4=1,RIGHT(AI$3,4)&amp;", ","")&amp;IF($AJ4=1,RIGHT(AJ$3,4)&amp;", ","")&amp;IF($AK4=1,RIGHT(AK$3,4)&amp;", ","")&amp;IF($AL4=1,RIGHT(AL$3,4)&amp;", ","")&amp;IF($AM4=1,RIGHT(AM$3,4)&amp;", ","")&amp;IF($AN4=1,RIGHT(AN$3,4)&amp;", ","")&amp;IF($AO4=1,RIGHT(AO$3,4)&amp;", ","")&amp;IF($AP4=1,RIGHT(AP$3,4)&amp;", ","")&amp;IF($AQ4=1,RIGHT(AQ$3,4)&amp;", ","")&amp;IF($AR4=1,RIGHT(AR$3,4)&amp;", ","")&amp;IF($AS4=1,RIGHT(AS$3,4)&amp;", ","")&amp;IF($AT4=1,RIGHT(AT$3,4)&amp;", ","")</f>
         <v xml:space="preserve">1997, 2000, 2003, 2010, 2015, </v>
       </c>
     </row>
-    <row r="5" spans="1:50">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <f t="shared" ref="A5:A36" si="1">1+A4</f>
         <v>2</v>
@@ -25462,15 +25473,16 @@
       <c r="AQ5" s="13"/>
       <c r="AR5" s="31"/>
       <c r="AS5" s="31"/>
-      <c r="AU5" s="2"/>
+      <c r="AT5" s="31"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
-      <c r="AX5" t="str">
-        <f t="shared" ref="AX5:AX68" si="2">+IF($F5=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G5=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H5=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I5=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J5=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K5=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L5=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M5=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N5=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O5=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P5=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q5=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R5=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S5=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T5=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U5=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V5=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W5=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X5=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y5=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z5=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA5=1,RIGHT(AA$3,4)&amp;", ","")&amp;IF($AB5=1,RIGHT(AB$3,4)&amp;", ","")&amp;IF($AC5=1,RIGHT(AC$3,4)&amp;", ","")&amp;IF($AD5=1,RIGHT(AD$3,4)&amp;", ","")&amp;IF($AE5=1,RIGHT(AE$3,4)&amp;", ","")&amp;IF($AF5=1,RIGHT(AF$3,4)&amp;", ","")&amp;IF($AG5=1,RIGHT(AG$3,4)&amp;", ","")&amp;IF($AH5=1,RIGHT(AH$3,4)&amp;", ","")&amp;IF($AI5=1,RIGHT(AI$3,4)&amp;", ","")&amp;IF($AJ5=1,RIGHT(AJ$3,4)&amp;", ","")&amp;IF($AK5=1,RIGHT(AK$3,4)&amp;", ","")&amp;IF($AL5=1,RIGHT(AL$3,4)&amp;", ","")&amp;IF($AM5=1,RIGHT(AM$3,4)&amp;", ","")&amp;IF($AN5=1,RIGHT(AN$3,4)&amp;", ","")&amp;IF($AO5=1,RIGHT(AO$3,4)&amp;", ","")&amp;IF($AP5=1,RIGHT(AP$3,4)&amp;", ","")&amp;IF($AQ5=1,RIGHT(AQ$3,4)&amp;", ","")&amp;IF($AR5=1,RIGHT(AR$3,4)&amp;", ","")&amp;IF($AS5=1,RIGHT(AS$3,4)&amp;", ","")</f>
+      <c r="AX5" s="2"/>
+      <c r="AY5" t="str">
+        <f t="shared" ref="AY5:AY68" si="2">+IF($F5=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G5=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H5=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I5=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J5=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K5=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L5=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M5=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N5=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O5=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P5=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q5=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R5=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S5=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T5=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U5=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V5=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W5=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X5=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y5=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z5=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA5=1,RIGHT(AA$3,4)&amp;", ","")&amp;IF($AB5=1,RIGHT(AB$3,4)&amp;", ","")&amp;IF($AC5=1,RIGHT(AC$3,4)&amp;", ","")&amp;IF($AD5=1,RIGHT(AD$3,4)&amp;", ","")&amp;IF($AE5=1,RIGHT(AE$3,4)&amp;", ","")&amp;IF($AF5=1,RIGHT(AF$3,4)&amp;", ","")&amp;IF($AG5=1,RIGHT(AG$3,4)&amp;", ","")&amp;IF($AH5=1,RIGHT(AH$3,4)&amp;", ","")&amp;IF($AI5=1,RIGHT(AI$3,4)&amp;", ","")&amp;IF($AJ5=1,RIGHT(AJ$3,4)&amp;", ","")&amp;IF($AK5=1,RIGHT(AK$3,4)&amp;", ","")&amp;IF($AL5=1,RIGHT(AL$3,4)&amp;", ","")&amp;IF($AM5=1,RIGHT(AM$3,4)&amp;", ","")&amp;IF($AN5=1,RIGHT(AN$3,4)&amp;", ","")&amp;IF($AO5=1,RIGHT(AO$3,4)&amp;", ","")&amp;IF($AP5=1,RIGHT(AP$3,4)&amp;", ","")&amp;IF($AQ5=1,RIGHT(AQ$3,4)&amp;", ","")&amp;IF($AR5=1,RIGHT(AR$3,4)&amp;", ","")&amp;IF($AS5=1,RIGHT(AS$3,4)&amp;", ","")&amp;IF($AT5=1,RIGHT(AT$3,4)&amp;", ","")</f>
         <v xml:space="preserve">1996, 2001, 2015, </v>
       </c>
     </row>
-    <row r="6" spans="1:50">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -25599,18 +25611,19 @@
       <c r="AQ6" s="13"/>
       <c r="AR6" s="13"/>
       <c r="AS6" s="13"/>
-      <c r="AT6" s="2" t="s">
+      <c r="AT6" s="13"/>
+      <c r="AU6" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
-      <c r="AX6" t="str">
+      <c r="AX6" s="2"/>
+      <c r="AY6" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2005, 2008, 2017, 2020, </v>
       </c>
     </row>
-    <row r="7" spans="1:50">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -25737,16 +25750,17 @@
       <c r="AQ7" s="13"/>
       <c r="AR7" s="13"/>
       <c r="AS7" s="13"/>
-      <c r="AT7" s="2"/>
+      <c r="AT7" s="13"/>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
-      <c r="AX7" t="str">
+      <c r="AX7" s="2"/>
+      <c r="AY7" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2011, 2019, </v>
       </c>
     </row>
-    <row r="8" spans="1:50">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -25873,16 +25887,17 @@
       <c r="AQ8" s="13"/>
       <c r="AR8" s="13"/>
       <c r="AS8" s="13"/>
-      <c r="AT8" s="2"/>
+      <c r="AT8" s="13"/>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
-      <c r="AX8" t="str">
+      <c r="AX8" s="2"/>
+      <c r="AY8" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2005, 2010, 2015, </v>
       </c>
     </row>
-    <row r="9" spans="1:50">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -26009,16 +26024,17 @@
       <c r="AQ9" s="13"/>
       <c r="AR9" s="13"/>
       <c r="AS9" s="13"/>
-      <c r="AT9" s="2"/>
+      <c r="AT9" s="13"/>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
-      <c r="AX9" t="str">
+      <c r="AX9" s="2"/>
+      <c r="AY9" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="16.149999999999999" customHeight="1">
+    <row r="10" spans="1:51" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -26145,16 +26161,17 @@
       <c r="AQ10" s="13"/>
       <c r="AR10" s="13"/>
       <c r="AS10" s="13"/>
-      <c r="AT10" s="2"/>
+      <c r="AT10" s="13"/>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
-      <c r="AX10" t="str">
+      <c r="AX10" s="2"/>
+      <c r="AY10" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2006, </v>
       </c>
     </row>
-    <row r="11" spans="1:50">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -26281,16 +26298,17 @@
       <c r="AQ11" s="13"/>
       <c r="AR11" s="13"/>
       <c r="AS11" s="13"/>
-      <c r="AT11" s="2"/>
+      <c r="AT11" s="13"/>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
-      <c r="AX11" t="str">
+      <c r="AX11" s="2"/>
+      <c r="AY11" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1987, 1996, 2000, 2005, 2010, 2016, </v>
       </c>
     </row>
-    <row r="12" spans="1:50">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -26417,16 +26435,17 @@
       <c r="AQ12" s="13"/>
       <c r="AR12" s="13"/>
       <c r="AS12" s="13"/>
-      <c r="AT12" s="2"/>
+      <c r="AT12" s="13"/>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
-      <c r="AX12" t="str">
+      <c r="AX12" s="2"/>
+      <c r="AY12" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2001, 2006, 2011, 2014, 2017, </v>
       </c>
     </row>
-    <row r="13" spans="1:50">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -26553,16 +26572,17 @@
       <c r="AQ13" s="13"/>
       <c r="AR13" s="13"/>
       <c r="AS13" s="13"/>
-      <c r="AT13" s="2"/>
+      <c r="AT13" s="13"/>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
-      <c r="AX13" t="str">
+      <c r="AX13" s="2"/>
+      <c r="AY13" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1993, 1996, 1999, 2006, 2010, </v>
       </c>
     </row>
-    <row r="14" spans="1:50">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -26689,16 +26709,17 @@
       <c r="AQ14" s="13"/>
       <c r="AR14" s="13"/>
       <c r="AS14" s="13"/>
-      <c r="AT14" s="2"/>
+      <c r="AT14" s="13"/>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
-      <c r="AX14" t="str">
+      <c r="AX14" s="2"/>
+      <c r="AY14" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1993, 1994, 1995, 1997, 2000, 2001, 2003, 2004, 2006, 2007, 2011, 2012, 2014, 2017, 2019, </v>
       </c>
     </row>
-    <row r="15" spans="1:50" s="23" customFormat="1">
+    <row r="15" spans="1:51" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="20">
         <f t="shared" si="1"/>
         <v>12</v>
@@ -26825,18 +26846,19 @@
       <c r="AQ15" s="19"/>
       <c r="AR15" s="19"/>
       <c r="AS15" s="19"/>
-      <c r="AT15" s="22" t="s">
+      <c r="AT15" s="19"/>
+      <c r="AU15" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="AU15" s="22"/>
       <c r="AV15" s="22"/>
       <c r="AW15" s="22"/>
-      <c r="AX15" t="str">
+      <c r="AX15" s="22"/>
+      <c r="AY15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2008, 2014, 2019, </v>
       </c>
     </row>
-    <row r="16" spans="1:50">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -26963,16 +26985,17 @@
       <c r="AQ16" s="13"/>
       <c r="AR16" s="13"/>
       <c r="AS16" s="13"/>
-      <c r="AT16" s="2"/>
+      <c r="AT16" s="13"/>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
-      <c r="AX16" t="str">
+      <c r="AX16" s="2"/>
+      <c r="AY16" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2003, 2006, 2011, </v>
       </c>
     </row>
-    <row r="17" spans="1:50">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -27099,16 +27122,17 @@
       <c r="AQ17" s="13"/>
       <c r="AR17" s="13"/>
       <c r="AS17" s="13"/>
-      <c r="AT17" s="2"/>
+      <c r="AT17" s="13"/>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
-      <c r="AX17" t="str">
+      <c r="AX17" s="2"/>
+      <c r="AY17" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2005, 2012, 2019, </v>
       </c>
     </row>
-    <row r="18" spans="1:50">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -27235,16 +27259,17 @@
       <c r="AQ18" s="13"/>
       <c r="AR18" s="13"/>
       <c r="AS18" s="13"/>
-      <c r="AT18" s="2"/>
+      <c r="AT18" s="13"/>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
-      <c r="AX18" t="str">
+      <c r="AX18" s="2"/>
+      <c r="AY18" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1998, 1999, 2006, 2011, 2015, </v>
       </c>
     </row>
-    <row r="19" spans="1:50">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -27371,16 +27396,17 @@
       <c r="AQ19" s="13"/>
       <c r="AR19" s="13"/>
       <c r="AS19" s="13"/>
-      <c r="AT19" s="2"/>
+      <c r="AT19" s="13"/>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
-      <c r="AX19" t="str">
+      <c r="AX19" s="2"/>
+      <c r="AY19" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1989, 1994, 1996, 1998, 2000, 2003, 2008, 2016, </v>
       </c>
     </row>
-    <row r="20" spans="1:50">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -27507,16 +27533,17 @@
       <c r="AQ20" s="13"/>
       <c r="AR20" s="13"/>
       <c r="AS20" s="13"/>
-      <c r="AT20" s="2"/>
+      <c r="AT20" s="13"/>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
-      <c r="AX20" t="str">
+      <c r="AX20" s="2"/>
+      <c r="AY20" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1986, 1991, 1996, 2003, 2013, 2019, </v>
       </c>
     </row>
-    <row r="21" spans="1:50">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -27643,16 +27670,17 @@
       <c r="AQ21" s="13"/>
       <c r="AR21" s="13"/>
       <c r="AS21" s="13"/>
-      <c r="AT21" s="2"/>
+      <c r="AT21" s="13"/>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
-      <c r="AX21" t="str">
+      <c r="AX21" s="2"/>
+      <c r="AY21" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2010, </v>
       </c>
     </row>
-    <row r="22" spans="1:50">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -27779,16 +27807,17 @@
       <c r="AQ22" s="13"/>
       <c r="AR22" s="13"/>
       <c r="AS22" s="13"/>
-      <c r="AT22" s="2"/>
+      <c r="AT22" s="13"/>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
-      <c r="AX22" t="str">
+      <c r="AX22" s="2"/>
+      <c r="AY22" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1988, 2000, 2007, </v>
       </c>
     </row>
-    <row r="23" spans="1:50">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -27915,16 +27944,17 @@
       <c r="AQ23" s="13"/>
       <c r="AR23" s="13"/>
       <c r="AS23" s="13"/>
-      <c r="AT23" s="2"/>
+      <c r="AT23" s="13"/>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
-      <c r="AX23" t="str">
+      <c r="AX23" s="2"/>
+      <c r="AY23" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1995, 1996, 2000, 2006, 2010, 2018, </v>
       </c>
     </row>
-    <row r="24" spans="1:50">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -28051,16 +28081,17 @@
       <c r="AQ24" s="13"/>
       <c r="AR24" s="13"/>
       <c r="AS24" s="13"/>
-      <c r="AT24" s="2"/>
+      <c r="AT24" s="13"/>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
-      <c r="AX24" t="str">
+      <c r="AX24" s="2"/>
+      <c r="AY24" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="17.45" customHeight="1">
+    <row r="25" spans="1:51" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <f t="shared" si="1"/>
         <v>22</v>
@@ -28187,16 +28218,17 @@
       <c r="AQ25" s="13"/>
       <c r="AR25" s="13"/>
       <c r="AS25" s="13"/>
-      <c r="AT25" s="2"/>
+      <c r="AT25" s="13"/>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
-      <c r="AX25" t="str">
+      <c r="AX25" s="2"/>
+      <c r="AY25" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1995, </v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="15.6" customHeight="1">
+    <row r="26" spans="1:51" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <f t="shared" si="1"/>
         <v>23</v>
@@ -28323,16 +28355,17 @@
       <c r="AQ26" s="13"/>
       <c r="AR26" s="13"/>
       <c r="AS26" s="13"/>
-      <c r="AT26" s="2"/>
+      <c r="AT26" s="13"/>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
-      <c r="AX26" t="str">
+      <c r="AX26" s="2"/>
+      <c r="AY26" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1994, 1996, 1999, 2000, 2003, 2006, 2012, 2016, </v>
       </c>
     </row>
-    <row r="27" spans="1:50">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <f t="shared" si="1"/>
         <v>24</v>
@@ -28459,16 +28492,17 @@
       <c r="AQ27" s="13"/>
       <c r="AR27" s="13"/>
       <c r="AS27" s="13"/>
-      <c r="AT27" s="2"/>
+      <c r="AT27" s="13"/>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
-      <c r="AX27" t="str">
+      <c r="AX27" s="2"/>
+      <c r="AY27" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1991, 1998, 2000, 2004, 2006, 2011, 2014, 2018, </v>
       </c>
     </row>
-    <row r="28" spans="1:50">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <f t="shared" si="1"/>
         <v>25</v>
@@ -28595,16 +28629,17 @@
       <c r="AQ28" s="13"/>
       <c r="AR28" s="13"/>
       <c r="AS28" s="13"/>
-      <c r="AT28" s="2"/>
+      <c r="AT28" s="13"/>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
-      <c r="AX28" t="str">
+      <c r="AX28" s="2"/>
+      <c r="AY28" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1995, 2001, 2007, 2010, 2013, 2017, </v>
       </c>
     </row>
-    <row r="29" spans="1:50">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <f t="shared" si="1"/>
         <v>26</v>
@@ -28731,16 +28766,17 @@
       <c r="AQ29" s="13"/>
       <c r="AR29" s="13"/>
       <c r="AS29" s="13"/>
-      <c r="AT29" s="2"/>
+      <c r="AT29" s="13"/>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
-      <c r="AX29" t="str">
+      <c r="AX29" s="2"/>
+      <c r="AY29" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2003, 2005, 2011, 2014, </v>
       </c>
     </row>
-    <row r="30" spans="1:50">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <f t="shared" si="1"/>
         <v>27</v>
@@ -28867,16 +28903,17 @@
       <c r="AQ30" s="13"/>
       <c r="AR30" s="13"/>
       <c r="AS30" s="13"/>
-      <c r="AT30" s="2"/>
+      <c r="AT30" s="13"/>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
-      <c r="AX30" t="str">
+      <c r="AX30" s="2"/>
+      <c r="AY30" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1986, 1990, 1995, 2000, 2005, 2010, 2015, </v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="17.45" customHeight="1">
+    <row r="31" spans="1:51" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <f t="shared" si="1"/>
         <v>28</v>
@@ -29003,16 +29040,17 @@
       <c r="AQ31" s="13"/>
       <c r="AR31" s="13"/>
       <c r="AS31" s="13"/>
-      <c r="AT31" s="2"/>
+      <c r="AT31" s="13"/>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
-      <c r="AX31" t="str">
+      <c r="AX31" s="2"/>
+      <c r="AY31" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2000, 2012, </v>
       </c>
     </row>
-    <row r="32" spans="1:50">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <f t="shared" si="1"/>
         <v>29</v>
@@ -29139,16 +29177,17 @@
       <c r="AQ32" s="13"/>
       <c r="AR32" s="13"/>
       <c r="AS32" s="13"/>
-      <c r="AT32" s="2"/>
+      <c r="AT32" s="13"/>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
-      <c r="AX32" t="str">
+      <c r="AX32" s="2"/>
+      <c r="AY32" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2005, </v>
       </c>
     </row>
-    <row r="33" spans="1:50">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <f t="shared" si="1"/>
         <v>30</v>
@@ -29275,16 +29314,17 @@
       <c r="AQ33" s="13"/>
       <c r="AR33" s="13"/>
       <c r="AS33" s="13"/>
-      <c r="AT33" s="2"/>
+      <c r="AT33" s="13"/>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>
-      <c r="AX33" t="str">
+      <c r="AX33" s="2"/>
+      <c r="AY33" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2011, 2018, </v>
       </c>
     </row>
-    <row r="34" spans="1:50">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <f t="shared" si="1"/>
         <v>31</v>
@@ -29411,16 +29451,17 @@
       <c r="AQ34" s="13"/>
       <c r="AR34" s="13"/>
       <c r="AS34" s="13"/>
-      <c r="AT34" s="2"/>
+      <c r="AT34" s="13"/>
       <c r="AU34" s="2"/>
       <c r="AV34" s="2"/>
       <c r="AW34" s="2"/>
-      <c r="AX34" t="str">
+      <c r="AX34" s="2"/>
+      <c r="AY34" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2006, </v>
       </c>
     </row>
-    <row r="35" spans="1:50">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <f t="shared" si="1"/>
         <v>32</v>
@@ -29547,16 +29588,17 @@
       <c r="AQ35" s="13"/>
       <c r="AR35" s="13"/>
       <c r="AS35" s="13"/>
-      <c r="AT35" s="2"/>
+      <c r="AT35" s="13"/>
       <c r="AU35" s="2"/>
       <c r="AV35" s="2"/>
       <c r="AW35" s="2"/>
-      <c r="AX35" t="str">
+      <c r="AX35" s="2"/>
+      <c r="AY35" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="16.899999999999999" customHeight="1">
+    <row r="36" spans="1:51" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <f t="shared" si="1"/>
         <v>33</v>
@@ -29683,16 +29725,17 @@
       <c r="AQ36" s="13"/>
       <c r="AR36" s="13"/>
       <c r="AS36" s="13"/>
-      <c r="AT36" s="2"/>
+      <c r="AT36" s="13"/>
       <c r="AU36" s="2"/>
       <c r="AV36" s="2"/>
       <c r="AW36" s="2"/>
-      <c r="AX36" t="str">
+      <c r="AX36" s="2"/>
+      <c r="AY36" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1986, 1991, 1996, 1999, 2000, 2002, 2003, 2007, 2013, 2014, 2019, </v>
       </c>
     </row>
-    <row r="37" spans="1:50">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <f t="shared" ref="A37:A68" si="3">1+A36</f>
         <v>34</v>
@@ -29819,16 +29862,17 @@
       <c r="AQ37" s="13"/>
       <c r="AR37" s="13"/>
       <c r="AS37" s="13"/>
-      <c r="AT37" s="2"/>
+      <c r="AT37" s="13"/>
       <c r="AU37" s="2"/>
       <c r="AV37" s="2"/>
       <c r="AW37" s="2"/>
-      <c r="AX37" t="str">
+      <c r="AX37" s="2"/>
+      <c r="AY37" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1995, 2000, 2006, 2012, 2018, </v>
       </c>
     </row>
-    <row r="38" spans="1:50">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <f t="shared" si="3"/>
         <v>35</v>
@@ -29955,16 +29999,17 @@
       <c r="AQ38" s="13"/>
       <c r="AR38" s="13"/>
       <c r="AS38" s="13"/>
-      <c r="AT38" s="2"/>
+      <c r="AT38" s="13"/>
       <c r="AU38" s="2"/>
       <c r="AV38" s="2"/>
       <c r="AW38" s="2"/>
-      <c r="AX38" t="str">
+      <c r="AX38" s="2"/>
+      <c r="AY38" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1987, 1999, 2003, 2004, </v>
       </c>
     </row>
-    <row r="39" spans="1:50">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <f t="shared" si="3"/>
         <v>36</v>
@@ -30093,16 +30138,17 @@
       <c r="AQ39" s="13"/>
       <c r="AR39" s="13"/>
       <c r="AS39" s="13"/>
-      <c r="AT39" s="2"/>
+      <c r="AT39" s="13"/>
       <c r="AU39" s="2"/>
       <c r="AV39" s="2"/>
       <c r="AW39" s="2"/>
-      <c r="AX39" t="str">
+      <c r="AX39" s="2"/>
+      <c r="AY39" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1988, 1992, 2000, 2005, 2008, 2014, 2021, </v>
       </c>
     </row>
-    <row r="40" spans="1:50" ht="19.899999999999999" customHeight="1">
+    <row r="40" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <f t="shared" si="3"/>
         <v>37</v>
@@ -30229,16 +30275,17 @@
       <c r="AQ40" s="13"/>
       <c r="AR40" s="13"/>
       <c r="AS40" s="13"/>
-      <c r="AT40" s="2"/>
+      <c r="AT40" s="13"/>
       <c r="AU40" s="2"/>
       <c r="AV40" s="2"/>
       <c r="AW40" s="2"/>
-      <c r="AX40" t="str">
+      <c r="AX40" s="2"/>
+      <c r="AY40" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1995, 2002, </v>
       </c>
     </row>
-    <row r="41" spans="1:50">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <f t="shared" si="3"/>
         <v>38</v>
@@ -30365,16 +30412,17 @@
       <c r="AQ41" s="13"/>
       <c r="AR41" s="13"/>
       <c r="AS41" s="13"/>
-      <c r="AT41" s="2"/>
+      <c r="AT41" s="13"/>
       <c r="AU41" s="2"/>
       <c r="AV41" s="2"/>
       <c r="AW41" s="2"/>
-      <c r="AX41" t="str">
+      <c r="AX41" s="2"/>
+      <c r="AY41" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1995, 2000, 2003, 2005, 2011, 2016, </v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="20.45" customHeight="1">
+    <row r="42" spans="1:51" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <f t="shared" si="3"/>
         <v>39</v>
@@ -30501,16 +30549,17 @@
       <c r="AQ42" s="13"/>
       <c r="AR42" s="13"/>
       <c r="AS42" s="13"/>
-      <c r="AT42" s="2"/>
+      <c r="AT42" s="13"/>
       <c r="AU42" s="2"/>
       <c r="AV42" s="2"/>
       <c r="AW42" s="2"/>
-      <c r="AX42" t="str">
+      <c r="AX42" s="2"/>
+      <c r="AY42" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:50">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <f t="shared" si="3"/>
         <v>40</v>
@@ -30637,16 +30686,17 @@
       <c r="AQ43" s="13"/>
       <c r="AR43" s="13"/>
       <c r="AS43" s="13"/>
-      <c r="AT43" s="2"/>
+      <c r="AT43" s="13"/>
       <c r="AU43" s="2"/>
       <c r="AV43" s="2"/>
       <c r="AW43" s="2"/>
-      <c r="AX43" t="str">
+      <c r="AX43" s="2"/>
+      <c r="AY43" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:50">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <f t="shared" si="3"/>
         <v>41</v>
@@ -30773,16 +30823,17 @@
       <c r="AQ44" s="13"/>
       <c r="AR44" s="13"/>
       <c r="AS44" s="13"/>
-      <c r="AT44" s="2"/>
+      <c r="AT44" s="13"/>
       <c r="AU44" s="2"/>
       <c r="AV44" s="2"/>
       <c r="AW44" s="2"/>
-      <c r="AX44" t="str">
+      <c r="AX44" s="2"/>
+      <c r="AY44" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2000, 2012, 2019, </v>
       </c>
     </row>
-    <row r="45" spans="1:50">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <f t="shared" si="3"/>
         <v>42</v>
@@ -30909,16 +30960,17 @@
       <c r="AQ45" s="13"/>
       <c r="AR45" s="13"/>
       <c r="AS45" s="13"/>
-      <c r="AT45" s="2"/>
+      <c r="AT45" s="13"/>
       <c r="AU45" s="2"/>
       <c r="AV45" s="2"/>
       <c r="AW45" s="2"/>
-      <c r="AX45" t="str">
+      <c r="AX45" s="2"/>
+      <c r="AY45" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1999, 2003, 2005, 2018, </v>
       </c>
     </row>
-    <row r="46" spans="1:50">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <f t="shared" si="3"/>
         <v>43</v>
@@ -31045,16 +31097,17 @@
       <c r="AQ46" s="13"/>
       <c r="AR46" s="13"/>
       <c r="AS46" s="13"/>
-      <c r="AT46" s="2"/>
+      <c r="AT46" s="13"/>
       <c r="AU46" s="2"/>
       <c r="AV46" s="2"/>
       <c r="AW46" s="2"/>
-      <c r="AX46" t="str">
+      <c r="AX46" s="2"/>
+      <c r="AY46" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1988, 1994, 1995, 1999, 2006, 2008, 2011, 2014, 2017, </v>
       </c>
     </row>
-    <row r="47" spans="1:50">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <f t="shared" si="3"/>
         <v>44</v>
@@ -31181,16 +31234,17 @@
       <c r="AQ47" s="13"/>
       <c r="AR47" s="13"/>
       <c r="AS47" s="13"/>
-      <c r="AT47" s="2"/>
+      <c r="AT47" s="13"/>
       <c r="AU47" s="2"/>
       <c r="AV47" s="2"/>
       <c r="AW47" s="2"/>
-      <c r="AX47" t="str">
+      <c r="AX47" s="2"/>
+      <c r="AY47" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 1999, 2005, 2012, 2016, 2018, </v>
       </c>
     </row>
-    <row r="48" spans="1:50">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
         <f t="shared" si="3"/>
         <v>45</v>
@@ -31317,16 +31371,17 @@
       <c r="AQ48" s="13"/>
       <c r="AR48" s="13"/>
       <c r="AS48" s="13"/>
-      <c r="AT48" s="2"/>
+      <c r="AT48" s="13"/>
       <c r="AU48" s="2"/>
       <c r="AV48" s="2"/>
       <c r="AW48" s="2"/>
-      <c r="AX48" t="str">
+      <c r="AX48" s="2"/>
+      <c r="AY48" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2000, 2005, 2010, 2013, 2018, 2019, </v>
       </c>
     </row>
-    <row r="49" spans="1:50">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <f t="shared" si="3"/>
         <v>46</v>
@@ -31453,16 +31508,17 @@
       <c r="AQ49" s="13"/>
       <c r="AR49" s="13"/>
       <c r="AS49" s="13"/>
-      <c r="AT49" s="2"/>
+      <c r="AT49" s="13"/>
       <c r="AU49" s="2"/>
       <c r="AV49" s="2"/>
       <c r="AW49" s="2"/>
-      <c r="AX49" t="str">
+      <c r="AX49" s="2"/>
+      <c r="AY49" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2002, 2006, 2010, 2014, 2018, </v>
       </c>
     </row>
-    <row r="50" spans="1:50">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <f t="shared" si="3"/>
         <v>47</v>
@@ -31589,16 +31645,17 @@
       <c r="AQ50" s="13"/>
       <c r="AR50" s="13"/>
       <c r="AS50" s="13"/>
-      <c r="AT50" s="2"/>
+      <c r="AT50" s="13"/>
       <c r="AU50" s="2"/>
       <c r="AV50" s="2"/>
       <c r="AW50" s="2"/>
-      <c r="AX50" t="str">
+      <c r="AX50" s="2"/>
+      <c r="AY50" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2011, </v>
       </c>
     </row>
-    <row r="51" spans="1:50">
+    <row r="51" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <f t="shared" si="3"/>
         <v>48</v>
@@ -31725,16 +31782,17 @@
       <c r="AQ51" s="13"/>
       <c r="AR51" s="13"/>
       <c r="AS51" s="13"/>
-      <c r="AT51" s="2"/>
+      <c r="AT51" s="13"/>
       <c r="AU51" s="2"/>
       <c r="AV51" s="2"/>
       <c r="AW51" s="2"/>
-      <c r="AX51" t="str">
+      <c r="AX51" s="2"/>
+      <c r="AY51" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:50">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A52" s="9">
         <f t="shared" si="3"/>
         <v>49</v>
@@ -31861,16 +31919,17 @@
       <c r="AQ52" s="13"/>
       <c r="AR52" s="13"/>
       <c r="AS52" s="13"/>
-      <c r="AT52" s="2"/>
+      <c r="AT52" s="13"/>
       <c r="AU52" s="2"/>
       <c r="AV52" s="2"/>
       <c r="AW52" s="2"/>
-      <c r="AX52" t="str">
+      <c r="AX52" s="2"/>
+      <c r="AY52" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1987, 1995, 2003, 2014, </v>
       </c>
     </row>
-    <row r="53" spans="1:50">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <f t="shared" si="3"/>
         <v>50</v>
@@ -31997,16 +32056,17 @@
       <c r="AQ53" s="13"/>
       <c r="AR53" s="13"/>
       <c r="AS53" s="13"/>
-      <c r="AT53" s="2"/>
+      <c r="AT53" s="13"/>
       <c r="AU53" s="2"/>
       <c r="AV53" s="2"/>
       <c r="AW53" s="2"/>
-      <c r="AX53" t="str">
+      <c r="AX53" s="2"/>
+      <c r="AY53" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2000, 2006, 2009, 2014, 2019, </v>
       </c>
     </row>
-    <row r="54" spans="1:50">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A54" s="9">
         <f t="shared" si="3"/>
         <v>51</v>
@@ -32133,16 +32193,17 @@
       <c r="AQ54" s="13"/>
       <c r="AR54" s="13"/>
       <c r="AS54" s="13"/>
-      <c r="AT54" s="2"/>
+      <c r="AT54" s="13"/>
       <c r="AU54" s="2"/>
       <c r="AV54" s="2"/>
       <c r="AW54" s="2"/>
-      <c r="AX54" t="str">
+      <c r="AX54" s="2"/>
+      <c r="AY54" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2005, 2011, 2019, </v>
       </c>
     </row>
-    <row r="55" spans="1:50" s="23" customFormat="1">
+    <row r="55" spans="1:51" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="20">
         <f t="shared" si="3"/>
         <v>52</v>
@@ -32269,16 +32330,17 @@
       <c r="AQ55" s="19"/>
       <c r="AR55" s="19"/>
       <c r="AS55" s="19"/>
-      <c r="AT55" s="22"/>
+      <c r="AT55" s="19"/>
       <c r="AU55" s="22"/>
       <c r="AV55" s="22"/>
       <c r="AW55" s="22"/>
-      <c r="AX55" t="str">
+      <c r="AX55" s="22"/>
+      <c r="AY55" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2014, 2019, </v>
       </c>
     </row>
-    <row r="56" spans="1:50">
+    <row r="56" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A56" s="9">
         <f t="shared" si="3"/>
         <v>53</v>
@@ -32405,16 +32467,17 @@
       <c r="AQ56" s="13"/>
       <c r="AR56" s="13"/>
       <c r="AS56" s="13"/>
-      <c r="AT56" s="2"/>
+      <c r="AT56" s="13"/>
       <c r="AU56" s="2"/>
       <c r="AV56" s="2"/>
       <c r="AW56" s="2"/>
-      <c r="AX56" t="str">
+      <c r="AX56" s="2"/>
+      <c r="AY56" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1995, 2000, 2005, 2012, 2016, </v>
       </c>
     </row>
-    <row r="57" spans="1:50">
+    <row r="57" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <f t="shared" si="3"/>
         <v>54</v>
@@ -32541,16 +32604,17 @@
       <c r="AQ57" s="13"/>
       <c r="AR57" s="13"/>
       <c r="AS57" s="13"/>
-      <c r="AT57" s="2"/>
+      <c r="AT57" s="13"/>
       <c r="AU57" s="2"/>
       <c r="AV57" s="2"/>
       <c r="AW57" s="2"/>
-      <c r="AX57" t="str">
+      <c r="AX57" s="2"/>
+      <c r="AY57" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1987, 1991, 1994, 1996, 1997, 2000, 2002, 2007, 2012, 2017, </v>
       </c>
     </row>
-    <row r="58" spans="1:50">
+    <row r="58" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A58" s="9">
         <f t="shared" si="3"/>
         <v>55</v>
@@ -32677,16 +32741,17 @@
       <c r="AQ58" s="13"/>
       <c r="AR58" s="13"/>
       <c r="AS58" s="13"/>
-      <c r="AT58" s="2"/>
+      <c r="AT58" s="13"/>
       <c r="AU58" s="2"/>
       <c r="AV58" s="2"/>
       <c r="AW58" s="2"/>
-      <c r="AX58" t="str">
+      <c r="AX58" s="2"/>
+      <c r="AY58" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1993, 1996, 1999, 2000, 2003, 2005, 2015, 2019, </v>
       </c>
     </row>
-    <row r="59" spans="1:50">
+    <row r="59" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <f t="shared" si="3"/>
         <v>56</v>
@@ -32813,16 +32878,17 @@
       <c r="AQ59" s="13"/>
       <c r="AR59" s="13"/>
       <c r="AS59" s="13"/>
-      <c r="AT59" s="2"/>
+      <c r="AT59" s="13"/>
       <c r="AU59" s="2"/>
       <c r="AV59" s="2"/>
       <c r="AW59" s="2"/>
-      <c r="AX59" t="str">
+      <c r="AX59" s="2"/>
+      <c r="AY59" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1995, 1997, 2000, </v>
       </c>
     </row>
-    <row r="60" spans="1:50">
+    <row r="60" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A60" s="9">
         <f t="shared" si="3"/>
         <v>57</v>
@@ -32949,16 +33015,17 @@
       <c r="AQ60" s="13"/>
       <c r="AR60" s="13"/>
       <c r="AS60" s="13"/>
-      <c r="AT60" s="2"/>
+      <c r="AT60" s="13"/>
       <c r="AU60" s="2"/>
       <c r="AV60" s="2"/>
       <c r="AW60" s="2"/>
-      <c r="AX60" t="str">
+      <c r="AX60" s="2"/>
+      <c r="AY60" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1996, 2000, 2006, 2011, 2018, </v>
       </c>
     </row>
-    <row r="61" spans="1:50">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <f t="shared" si="3"/>
         <v>58</v>
@@ -33085,16 +33152,17 @@
       <c r="AQ61" s="13"/>
       <c r="AR61" s="13"/>
       <c r="AS61" s="13"/>
-      <c r="AT61" s="2"/>
+      <c r="AT61" s="13"/>
       <c r="AU61" s="2"/>
       <c r="AV61" s="2"/>
       <c r="AW61" s="2"/>
-      <c r="AX61" t="str">
+      <c r="AX61" s="2"/>
+      <c r="AY61" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2005, 2011, </v>
       </c>
     </row>
-    <row r="62" spans="1:50">
+    <row r="62" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A62" s="9">
         <f t="shared" si="3"/>
         <v>59</v>
@@ -33221,16 +33289,17 @@
       <c r="AQ62" s="13"/>
       <c r="AR62" s="13"/>
       <c r="AS62" s="13"/>
-      <c r="AT62" s="2"/>
+      <c r="AT62" s="13"/>
       <c r="AU62" s="2"/>
       <c r="AV62" s="2"/>
       <c r="AW62" s="2"/>
-      <c r="AX62" t="str">
+      <c r="AX62" s="2"/>
+      <c r="AY62" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1990, 1997, 2002, 2007, 2012, 2017, </v>
       </c>
     </row>
-    <row r="63" spans="1:50">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <f t="shared" si="3"/>
         <v>60</v>
@@ -33357,16 +33426,17 @@
       <c r="AQ63" s="13"/>
       <c r="AR63" s="13"/>
       <c r="AS63" s="13"/>
-      <c r="AT63" s="2"/>
+      <c r="AT63" s="13"/>
       <c r="AU63" s="2"/>
       <c r="AV63" s="2"/>
       <c r="AW63" s="2"/>
-      <c r="AX63" t="str">
+      <c r="AX63" s="2"/>
+      <c r="AY63" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1995, 1999, 2003, 2006, 2010, 2015, </v>
       </c>
     </row>
-    <row r="64" spans="1:50">
+    <row r="64" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A64" s="9">
         <f t="shared" si="3"/>
         <v>61</v>
@@ -33493,16 +33563,17 @@
       <c r="AQ64" s="13"/>
       <c r="AR64" s="13"/>
       <c r="AS64" s="13"/>
-      <c r="AT64" s="2"/>
+      <c r="AT64" s="13"/>
       <c r="AU64" s="2"/>
       <c r="AV64" s="2"/>
       <c r="AW64" s="2"/>
-      <c r="AX64" t="str">
+      <c r="AX64" s="2"/>
+      <c r="AY64" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1989, 1993, 1998, 2000, 2008, 2014, </v>
       </c>
     </row>
-    <row r="65" spans="1:50">
+    <row r="65" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <f t="shared" si="3"/>
         <v>62</v>
@@ -33629,16 +33700,17 @@
       <c r="AQ65" s="13"/>
       <c r="AR65" s="13"/>
       <c r="AS65" s="13"/>
-      <c r="AT65" s="2"/>
+      <c r="AT65" s="13"/>
       <c r="AU65" s="2"/>
       <c r="AV65" s="2"/>
       <c r="AW65" s="2"/>
-      <c r="AX65" t="str">
+      <c r="AX65" s="2"/>
+      <c r="AY65" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1995, 1997, 2005, 2012, 2014, 2018, </v>
       </c>
     </row>
-    <row r="66" spans="1:50">
+    <row r="66" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A66" s="9">
         <f t="shared" si="3"/>
         <v>63</v>
@@ -33765,16 +33837,17 @@
       <c r="AQ66" s="13"/>
       <c r="AR66" s="13"/>
       <c r="AS66" s="13"/>
-      <c r="AT66" s="2"/>
+      <c r="AT66" s="13"/>
       <c r="AU66" s="2"/>
       <c r="AV66" s="2"/>
       <c r="AW66" s="2"/>
-      <c r="AX66" t="str">
+      <c r="AX66" s="2"/>
+      <c r="AY66" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">1998, 2000, 2005, 2010, 2014, </v>
       </c>
     </row>
-    <row r="67" spans="1:50">
+    <row r="67" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A67" s="9">
         <f t="shared" si="3"/>
         <v>64</v>
@@ -33901,16 +33974,17 @@
       <c r="AQ67" s="13"/>
       <c r="AR67" s="13"/>
       <c r="AS67" s="13"/>
-      <c r="AT67" s="2"/>
+      <c r="AT67" s="13"/>
       <c r="AU67" s="2"/>
       <c r="AV67" s="2"/>
       <c r="AW67" s="2"/>
-      <c r="AX67" t="str">
+      <c r="AX67" s="2"/>
+      <c r="AY67" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">2009, 2014, 2018, </v>
       </c>
     </row>
-    <row r="68" spans="1:50">
+    <row r="68" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A68" s="9">
         <f t="shared" si="3"/>
         <v>65</v>
@@ -34037,16 +34111,17 @@
       <c r="AQ68" s="13"/>
       <c r="AR68" s="13"/>
       <c r="AS68" s="13"/>
-      <c r="AT68" s="2"/>
+      <c r="AT68" s="13"/>
       <c r="AU68" s="2"/>
       <c r="AV68" s="2"/>
       <c r="AW68" s="2"/>
-      <c r="AX68" t="str">
+      <c r="AX68" s="2"/>
+      <c r="AY68" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:50">
+    <row r="69" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A69" s="9">
         <f t="shared" ref="A69:A100" si="4">1+A68</f>
         <v>66</v>
@@ -34173,16 +34248,17 @@
       <c r="AQ69" s="13"/>
       <c r="AR69" s="13"/>
       <c r="AS69" s="13"/>
-      <c r="AT69" s="2"/>
+      <c r="AT69" s="13"/>
       <c r="AU69" s="2"/>
       <c r="AV69" s="2"/>
       <c r="AW69" s="2"/>
-      <c r="AX69" t="str">
-        <f t="shared" ref="AX69:AX132" si="5">+IF($F69=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G69=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H69=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I69=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J69=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K69=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L69=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M69=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N69=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O69=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P69=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q69=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R69=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S69=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T69=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U69=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V69=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W69=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X69=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y69=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z69=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA69=1,RIGHT(AA$3,4)&amp;", ","")&amp;IF($AB69=1,RIGHT(AB$3,4)&amp;", ","")&amp;IF($AC69=1,RIGHT(AC$3,4)&amp;", ","")&amp;IF($AD69=1,RIGHT(AD$3,4)&amp;", ","")&amp;IF($AE69=1,RIGHT(AE$3,4)&amp;", ","")&amp;IF($AF69=1,RIGHT(AF$3,4)&amp;", ","")&amp;IF($AG69=1,RIGHT(AG$3,4)&amp;", ","")&amp;IF($AH69=1,RIGHT(AH$3,4)&amp;", ","")&amp;IF($AI69=1,RIGHT(AI$3,4)&amp;", ","")&amp;IF($AJ69=1,RIGHT(AJ$3,4)&amp;", ","")&amp;IF($AK69=1,RIGHT(AK$3,4)&amp;", ","")&amp;IF($AL69=1,RIGHT(AL$3,4)&amp;", ","")&amp;IF($AM69=1,RIGHT(AM$3,4)&amp;", ","")&amp;IF($AN69=1,RIGHT(AN$3,4)&amp;", ","")&amp;IF($AO69=1,RIGHT(AO$3,4)&amp;", ","")&amp;IF($AP69=1,RIGHT(AP$3,4)&amp;", ","")&amp;IF($AQ69=1,RIGHT(AQ$3,4)&amp;", ","")&amp;IF($AR69=1,RIGHT(AR$3,4)&amp;", ","")&amp;IF($AS69=1,RIGHT(AS$3,4)&amp;", ","")</f>
+      <c r="AX69" s="2"/>
+      <c r="AY69" t="str">
+        <f t="shared" ref="AY69:AY132" si="5">+IF($F69=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G69=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H69=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I69=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J69=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K69=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L69=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M69=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N69=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O69=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P69=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q69=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R69=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S69=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T69=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U69=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V69=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W69=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X69=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y69=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z69=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA69=1,RIGHT(AA$3,4)&amp;", ","")&amp;IF($AB69=1,RIGHT(AB$3,4)&amp;", ","")&amp;IF($AC69=1,RIGHT(AC$3,4)&amp;", ","")&amp;IF($AD69=1,RIGHT(AD$3,4)&amp;", ","")&amp;IF($AE69=1,RIGHT(AE$3,4)&amp;", ","")&amp;IF($AF69=1,RIGHT(AF$3,4)&amp;", ","")&amp;IF($AG69=1,RIGHT(AG$3,4)&amp;", ","")&amp;IF($AH69=1,RIGHT(AH$3,4)&amp;", ","")&amp;IF($AI69=1,RIGHT(AI$3,4)&amp;", ","")&amp;IF($AJ69=1,RIGHT(AJ$3,4)&amp;", ","")&amp;IF($AK69=1,RIGHT(AK$3,4)&amp;", ","")&amp;IF($AL69=1,RIGHT(AL$3,4)&amp;", ","")&amp;IF($AM69=1,RIGHT(AM$3,4)&amp;", ","")&amp;IF($AN69=1,RIGHT(AN$3,4)&amp;", ","")&amp;IF($AO69=1,RIGHT(AO$3,4)&amp;", ","")&amp;IF($AP69=1,RIGHT(AP$3,4)&amp;", ","")&amp;IF($AQ69=1,RIGHT(AQ$3,4)&amp;", ","")&amp;IF($AR69=1,RIGHT(AR$3,4)&amp;", ","")&amp;IF($AS69=1,RIGHT(AS$3,4)&amp;", ","")&amp;IF($AT69=1,RIGHT(AT$3,4)&amp;", ","")</f>
         <v xml:space="preserve">1996, 2000, 2003, 2006, 2011, 2017, </v>
       </c>
     </row>
-    <row r="70" spans="1:50">
+    <row r="70" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A70" s="9">
         <f t="shared" si="4"/>
         <v>67</v>
@@ -34309,16 +34385,17 @@
       <c r="AQ70" s="13"/>
       <c r="AR70" s="13"/>
       <c r="AS70" s="13"/>
-      <c r="AT70" s="2"/>
+      <c r="AT70" s="13"/>
       <c r="AU70" s="2"/>
       <c r="AV70" s="2"/>
       <c r="AW70" s="2"/>
-      <c r="AX70" t="str">
+      <c r="AX70" s="2"/>
+      <c r="AY70" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2000, 2006, </v>
       </c>
     </row>
-    <row r="71" spans="1:50">
+    <row r="71" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A71" s="9">
         <f t="shared" si="4"/>
         <v>68</v>
@@ -34445,16 +34522,17 @@
       <c r="AQ71" s="13"/>
       <c r="AR71" s="13"/>
       <c r="AS71" s="13"/>
-      <c r="AT71" s="2"/>
+      <c r="AT71" s="13"/>
       <c r="AU71" s="2"/>
       <c r="AV71" s="2"/>
       <c r="AW71" s="2"/>
-      <c r="AX71" t="str">
+      <c r="AX71" s="2"/>
+      <c r="AY71" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1986, 1995, 2007, 2013, 2019, </v>
       </c>
     </row>
-    <row r="72" spans="1:50">
+    <row r="72" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A72" s="9">
         <f t="shared" si="4"/>
         <v>69</v>
@@ -34581,16 +34659,17 @@
       <c r="AQ72" s="13"/>
       <c r="AR72" s="13"/>
       <c r="AS72" s="13"/>
-      <c r="AT72" s="2"/>
+      <c r="AT72" s="13"/>
       <c r="AU72" s="2"/>
       <c r="AV72" s="2"/>
       <c r="AW72" s="2"/>
-      <c r="AX72" t="str">
+      <c r="AX72" s="2"/>
+      <c r="AY72" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2003, </v>
       </c>
     </row>
-    <row r="73" spans="1:50">
+    <row r="73" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A73" s="9">
         <f t="shared" si="4"/>
         <v>70</v>
@@ -34717,16 +34796,17 @@
       <c r="AQ73" s="13"/>
       <c r="AR73" s="13"/>
       <c r="AS73" s="13"/>
-      <c r="AT73" s="2"/>
+      <c r="AT73" s="13"/>
       <c r="AU73" s="2"/>
       <c r="AV73" s="2"/>
       <c r="AW73" s="2"/>
-      <c r="AX73" t="str">
+      <c r="AX73" s="2"/>
+      <c r="AY73" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2012, </v>
       </c>
     </row>
-    <row r="74" spans="1:50">
+    <row r="74" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A74" s="9">
         <f t="shared" si="4"/>
         <v>71</v>
@@ -34853,16 +34933,17 @@
       <c r="AQ74" s="13"/>
       <c r="AR74" s="13"/>
       <c r="AS74" s="13"/>
-      <c r="AT74" s="2"/>
+      <c r="AT74" s="13"/>
       <c r="AU74" s="2"/>
       <c r="AV74" s="2"/>
       <c r="AW74" s="2"/>
-      <c r="AX74" t="str">
+      <c r="AX74" s="2"/>
+      <c r="AY74" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1987, 2006, </v>
       </c>
     </row>
-    <row r="75" spans="1:50">
+    <row r="75" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A75" s="9">
         <f t="shared" si="4"/>
         <v>72</v>
@@ -34989,16 +35070,17 @@
       <c r="AQ75" s="13"/>
       <c r="AR75" s="13"/>
       <c r="AS75" s="13"/>
-      <c r="AT75" s="2"/>
+      <c r="AT75" s="13"/>
       <c r="AU75" s="2"/>
       <c r="AV75" s="2"/>
       <c r="AW75" s="2"/>
-      <c r="AX75" t="str">
+      <c r="AX75" s="2"/>
+      <c r="AY75" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1996, 2000, 2004, 2009, 2014, 2018, </v>
       </c>
     </row>
-    <row r="76" spans="1:50">
+    <row r="76" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A76" s="9">
         <f t="shared" si="4"/>
         <v>73</v>
@@ -35125,16 +35207,17 @@
       <c r="AQ76" s="13"/>
       <c r="AR76" s="13"/>
       <c r="AS76" s="13"/>
-      <c r="AT76" s="2"/>
+      <c r="AT76" s="13"/>
       <c r="AU76" s="2"/>
       <c r="AV76" s="2"/>
       <c r="AW76" s="2"/>
-      <c r="AX76" t="str">
+      <c r="AX76" s="2"/>
+      <c r="AY76" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1987, 1992, 1995, 2003, 2006, </v>
       </c>
     </row>
-    <row r="77" spans="1:50">
+    <row r="77" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A77" s="9">
         <f t="shared" si="4"/>
         <v>74</v>
@@ -35261,16 +35344,17 @@
       <c r="AQ77" s="13"/>
       <c r="AR77" s="13"/>
       <c r="AS77" s="13"/>
-      <c r="AT77" s="2"/>
+      <c r="AT77" s="13"/>
       <c r="AU77" s="2"/>
       <c r="AV77" s="2"/>
       <c r="AW77" s="2"/>
-      <c r="AX77" t="str">
+      <c r="AX77" s="2"/>
+      <c r="AY77" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2000, 2005, 2012, </v>
       </c>
     </row>
-    <row r="78" spans="1:50">
+    <row r="78" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A78" s="9">
         <f t="shared" si="4"/>
         <v>75</v>
@@ -35397,16 +35481,17 @@
       <c r="AQ78" s="13"/>
       <c r="AR78" s="13"/>
       <c r="AS78" s="13"/>
-      <c r="AT78" s="2"/>
+      <c r="AT78" s="13"/>
       <c r="AU78" s="2"/>
       <c r="AV78" s="2"/>
       <c r="AW78" s="2"/>
-      <c r="AX78" t="str">
+      <c r="AX78" s="2"/>
+      <c r="AY78" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1992, 1995, 1997, 2000, 2003, 2008, 2018, </v>
       </c>
     </row>
-    <row r="79" spans="1:50">
+    <row r="79" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A79" s="9">
         <f t="shared" si="4"/>
         <v>76</v>
@@ -35533,16 +35618,17 @@
       <c r="AQ79" s="13"/>
       <c r="AR79" s="13"/>
       <c r="AS79" s="13"/>
-      <c r="AT79" s="2"/>
+      <c r="AT79" s="13"/>
       <c r="AU79" s="2"/>
       <c r="AV79" s="2"/>
       <c r="AW79" s="2"/>
-      <c r="AX79" t="str">
+      <c r="AX79" s="2"/>
+      <c r="AY79" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1995, 2001, 2009, 2016, </v>
       </c>
     </row>
-    <row r="80" spans="1:50">
+    <row r="80" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A80" s="9">
         <f t="shared" si="4"/>
         <v>77</v>
@@ -35669,16 +35755,17 @@
       <c r="AQ80" s="13"/>
       <c r="AR80" s="13"/>
       <c r="AS80" s="13"/>
-      <c r="AT80" s="2"/>
+      <c r="AT80" s="13"/>
       <c r="AU80" s="2"/>
       <c r="AV80" s="2"/>
       <c r="AW80" s="2"/>
-      <c r="AX80" t="str">
+      <c r="AX80" s="2"/>
+      <c r="AY80" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1987, 2015, </v>
       </c>
     </row>
-    <row r="81" spans="1:50">
+    <row r="81" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A81" s="9">
         <f t="shared" si="4"/>
         <v>78</v>
@@ -35805,16 +35892,17 @@
       <c r="AQ81" s="13"/>
       <c r="AR81" s="13"/>
       <c r="AS81" s="13"/>
-      <c r="AT81" s="2"/>
+      <c r="AT81" s="13"/>
       <c r="AU81" s="2"/>
       <c r="AV81" s="2"/>
       <c r="AW81" s="2"/>
-      <c r="AX81" t="str">
+      <c r="AX81" s="2"/>
+      <c r="AY81" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2007, </v>
       </c>
     </row>
-    <row r="82" spans="1:50">
+    <row r="82" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A82" s="9">
         <f t="shared" si="4"/>
         <v>79</v>
@@ -35941,16 +36029,17 @@
       <c r="AQ82" s="13"/>
       <c r="AR82" s="13"/>
       <c r="AS82" s="13"/>
-      <c r="AT82" s="2"/>
+      <c r="AT82" s="13"/>
       <c r="AU82" s="2"/>
       <c r="AV82" s="2"/>
       <c r="AW82" s="2"/>
-      <c r="AX82" t="str">
+      <c r="AX82" s="2"/>
+      <c r="AY82" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1999, 2005, 2011, 2018, </v>
       </c>
     </row>
-    <row r="83" spans="1:50">
+    <row r="83" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A83" s="9">
         <f t="shared" si="4"/>
         <v>80</v>
@@ -36077,16 +36166,17 @@
       <c r="AQ83" s="13"/>
       <c r="AR83" s="13"/>
       <c r="AS83" s="13"/>
-      <c r="AT83" s="2"/>
+      <c r="AT83" s="13"/>
       <c r="AU83" s="2"/>
       <c r="AV83" s="2"/>
       <c r="AW83" s="2"/>
-      <c r="AX83" t="str">
+      <c r="AX83" s="2"/>
+      <c r="AY83" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1987, 1995, 1996, 2001, 2006, 2009, 2012, 2015, 2018, </v>
       </c>
     </row>
-    <row r="84" spans="1:50">
+    <row r="84" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A84" s="9">
         <f t="shared" si="4"/>
         <v>81</v>
@@ -36213,16 +36303,17 @@
       <c r="AQ84" s="13"/>
       <c r="AR84" s="13"/>
       <c r="AS84" s="13"/>
-      <c r="AT84" s="2"/>
+      <c r="AT84" s="13"/>
       <c r="AU84" s="2"/>
       <c r="AV84" s="2"/>
       <c r="AW84" s="2"/>
-      <c r="AX84" t="str">
+      <c r="AX84" s="2"/>
+      <c r="AY84" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1995, 2000, 2009, 2015, </v>
       </c>
     </row>
-    <row r="85" spans="1:50">
+    <row r="85" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A85" s="9">
         <f t="shared" si="4"/>
         <v>82</v>
@@ -36349,16 +36440,17 @@
       <c r="AQ85" s="13"/>
       <c r="AR85" s="13"/>
       <c r="AS85" s="13"/>
-      <c r="AT85" s="2"/>
+      <c r="AT85" s="13"/>
       <c r="AU85" s="2"/>
       <c r="AV85" s="2"/>
       <c r="AW85" s="2"/>
-      <c r="AX85" t="str">
+      <c r="AX85" s="2"/>
+      <c r="AY85" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2005, 2013, 2018, </v>
       </c>
     </row>
-    <row r="86" spans="1:50">
+    <row r="86" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A86" s="9">
         <f t="shared" si="4"/>
         <v>83</v>
@@ -36485,16 +36577,17 @@
       <c r="AQ86" s="13"/>
       <c r="AR86" s="13"/>
       <c r="AS86" s="13"/>
-      <c r="AT86" s="2"/>
+      <c r="AT86" s="13"/>
       <c r="AU86" s="2"/>
       <c r="AV86" s="2"/>
       <c r="AW86" s="2"/>
-      <c r="AX86" t="str">
+      <c r="AX86" s="2"/>
+      <c r="AY86" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1996, 2000, 2005, 2010, 2013, 2018, </v>
       </c>
     </row>
-    <row r="87" spans="1:50">
+    <row r="87" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A87" s="9">
         <f t="shared" si="4"/>
         <v>84</v>
@@ -36621,16 +36714,17 @@
       <c r="AQ87" s="13"/>
       <c r="AR87" s="13"/>
       <c r="AS87" s="13"/>
-      <c r="AT87" s="2"/>
+      <c r="AT87" s="13"/>
       <c r="AU87" s="2"/>
       <c r="AV87" s="2"/>
       <c r="AW87" s="2"/>
-      <c r="AX87" t="str">
+      <c r="AX87" s="2"/>
+      <c r="AY87" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1995, 1997, 2004, 2008, 2011, </v>
       </c>
     </row>
-    <row r="88" spans="1:50">
+    <row r="88" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A88" s="9">
         <f t="shared" si="4"/>
         <v>85</v>
@@ -36757,16 +36851,17 @@
       <c r="AQ88" s="13"/>
       <c r="AR88" s="13"/>
       <c r="AS88" s="13"/>
-      <c r="AT88" s="2"/>
+      <c r="AT88" s="13"/>
       <c r="AU88" s="2"/>
       <c r="AV88" s="2"/>
       <c r="AW88" s="2"/>
-      <c r="AX88" t="str">
+      <c r="AX88" s="2"/>
+      <c r="AY88" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1995, 2000, 2004, 2007, 2011, 2015, 2019, </v>
       </c>
     </row>
-    <row r="89" spans="1:50">
+    <row r="89" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A89" s="9">
         <f t="shared" si="4"/>
         <v>86</v>
@@ -36893,16 +36988,17 @@
       <c r="AQ89" s="13"/>
       <c r="AR89" s="13"/>
       <c r="AS89" s="13"/>
-      <c r="AT89" s="2"/>
+      <c r="AT89" s="13"/>
       <c r="AU89" s="2"/>
       <c r="AV89" s="2"/>
       <c r="AW89" s="2"/>
-      <c r="AX89" t="str">
+      <c r="AX89" s="2"/>
+      <c r="AY89" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:50">
+    <row r="90" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A90" s="9">
         <f t="shared" si="4"/>
         <v>87</v>
@@ -37029,16 +37125,17 @@
       <c r="AQ90" s="13"/>
       <c r="AR90" s="13"/>
       <c r="AS90" s="13"/>
-      <c r="AT90" s="2"/>
+      <c r="AT90" s="13"/>
       <c r="AU90" s="2"/>
       <c r="AV90" s="2"/>
       <c r="AW90" s="2"/>
-      <c r="AX90" t="str">
+      <c r="AX90" s="2"/>
+      <c r="AY90" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1992, 1995, 2000, 2004, 2006, 2010, 2013, 2015, 2019, </v>
       </c>
     </row>
-    <row r="91" spans="1:50">
+    <row r="91" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A91" s="9">
         <f t="shared" si="4"/>
         <v>88</v>
@@ -37165,16 +37262,17 @@
       <c r="AQ91" s="13"/>
       <c r="AR91" s="13"/>
       <c r="AS91" s="13"/>
-      <c r="AT91" s="2"/>
+      <c r="AT91" s="13"/>
       <c r="AU91" s="2"/>
       <c r="AV91" s="2"/>
       <c r="AW91" s="2"/>
-      <c r="AX91" t="str">
+      <c r="AX91" s="2"/>
+      <c r="AY91" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50">
+    <row r="92" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A92" s="9">
         <f t="shared" si="4"/>
         <v>89</v>
@@ -37301,16 +37399,17 @@
       <c r="AQ92" s="13"/>
       <c r="AR92" s="13"/>
       <c r="AS92" s="13"/>
-      <c r="AT92" s="2"/>
+      <c r="AT92" s="13"/>
       <c r="AU92" s="2"/>
       <c r="AV92" s="2"/>
       <c r="AW92" s="2"/>
-      <c r="AX92" t="str">
+      <c r="AX92" s="2"/>
+      <c r="AY92" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1992, 2000, 2006, 2013, </v>
       </c>
     </row>
-    <row r="93" spans="1:50">
+    <row r="93" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A93" s="9">
         <f t="shared" si="4"/>
         <v>90</v>
@@ -37439,16 +37538,17 @@
       <c r="AQ93" s="13"/>
       <c r="AR93" s="13"/>
       <c r="AS93" s="13"/>
-      <c r="AT93" s="2"/>
+      <c r="AT93" s="13"/>
       <c r="AU93" s="2"/>
       <c r="AV93" s="2"/>
       <c r="AW93" s="2"/>
-      <c r="AX93" t="str">
+      <c r="AX93" s="2"/>
+      <c r="AY93" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1992, 1996, 1998, 2000, 2006, 2012, 2017, 2021, </v>
       </c>
     </row>
-    <row r="94" spans="1:50">
+    <row r="94" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A94" s="9">
         <f t="shared" si="4"/>
         <v>91</v>
@@ -37575,16 +37675,17 @@
       <c r="AQ94" s="13"/>
       <c r="AR94" s="13"/>
       <c r="AS94" s="13"/>
-      <c r="AT94" s="2"/>
+      <c r="AT94" s="13"/>
       <c r="AU94" s="2"/>
       <c r="AV94" s="2"/>
       <c r="AW94" s="2"/>
-      <c r="AX94" t="str">
+      <c r="AX94" s="2"/>
+      <c r="AY94" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1990, 1995, 2003, 2007, 2008, 2011, 2013, 2014, 2015, 2016, 2018, </v>
       </c>
     </row>
-    <row r="95" spans="1:50">
+    <row r="95" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A95" s="9">
         <f t="shared" si="4"/>
         <v>92</v>
@@ -37711,16 +37812,17 @@
       <c r="AQ95" s="13"/>
       <c r="AR95" s="13"/>
       <c r="AS95" s="13"/>
-      <c r="AT95" s="2"/>
+      <c r="AT95" s="13"/>
       <c r="AU95" s="2"/>
       <c r="AV95" s="2"/>
       <c r="AW95" s="2"/>
-      <c r="AX95" t="str">
+      <c r="AX95" s="2"/>
+      <c r="AY95" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1998, 2001, 2007, </v>
       </c>
     </row>
-    <row r="96" spans="1:50">
+    <row r="96" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A96" s="9">
         <f t="shared" si="4"/>
         <v>93</v>
@@ -37847,16 +37949,17 @@
       <c r="AQ96" s="13"/>
       <c r="AR96" s="13"/>
       <c r="AS96" s="13"/>
-      <c r="AT96" s="2"/>
+      <c r="AT96" s="13"/>
       <c r="AU96" s="2"/>
       <c r="AV96" s="2"/>
       <c r="AW96" s="2"/>
-      <c r="AX96" t="str">
+      <c r="AX96" s="2"/>
+      <c r="AY96" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1995, 1996, 2001, 2006, 2011, 2014, 2016, 2019, </v>
       </c>
     </row>
-    <row r="97" spans="1:50">
+    <row r="97" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A97" s="9">
         <f t="shared" si="4"/>
         <v>94</v>
@@ -37983,16 +38086,17 @@
       <c r="AQ97" s="13"/>
       <c r="AR97" s="13"/>
       <c r="AS97" s="13"/>
-      <c r="AT97" s="2"/>
+      <c r="AT97" s="13"/>
       <c r="AU97" s="2"/>
       <c r="AV97" s="2"/>
       <c r="AW97" s="2"/>
-      <c r="AX97" t="str">
+      <c r="AX97" s="2"/>
+      <c r="AY97" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:50">
+    <row r="98" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A98" s="9">
         <f t="shared" si="4"/>
         <v>95</v>
@@ -38119,16 +38223,17 @@
       <c r="AQ98" s="13"/>
       <c r="AR98" s="13"/>
       <c r="AS98" s="13"/>
-      <c r="AT98" s="2"/>
+      <c r="AT98" s="13"/>
       <c r="AU98" s="2"/>
       <c r="AV98" s="2"/>
       <c r="AW98" s="2"/>
-      <c r="AX98" t="str">
+      <c r="AX98" s="2"/>
+      <c r="AY98" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1990, 1995, 2006, 2012, 2017, </v>
       </c>
     </row>
-    <row r="99" spans="1:50">
+    <row r="99" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A99" s="9">
         <f t="shared" si="4"/>
         <v>96</v>
@@ -38255,16 +38360,17 @@
       <c r="AQ99" s="13"/>
       <c r="AR99" s="13"/>
       <c r="AS99" s="13"/>
-      <c r="AT99" s="2"/>
+      <c r="AT99" s="13"/>
       <c r="AU99" s="2"/>
       <c r="AV99" s="2"/>
       <c r="AW99" s="2"/>
-      <c r="AX99" t="str">
+      <c r="AX99" s="2"/>
+      <c r="AY99" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1996, 2013, </v>
       </c>
     </row>
-    <row r="100" spans="1:50">
+    <row r="100" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A100" s="9">
         <f t="shared" si="4"/>
         <v>97</v>
@@ -38391,16 +38497,17 @@
       <c r="AQ100" s="13"/>
       <c r="AR100" s="13"/>
       <c r="AS100" s="13"/>
-      <c r="AT100" s="2"/>
+      <c r="AT100" s="13"/>
       <c r="AU100" s="2"/>
       <c r="AV100" s="2"/>
       <c r="AW100" s="2"/>
-      <c r="AX100" t="str">
+      <c r="AX100" s="2"/>
+      <c r="AY100" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1986, 1991, 1996, 2000, 2018, </v>
       </c>
     </row>
-    <row r="101" spans="1:50">
+    <row r="101" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A101" s="9">
         <f t="shared" ref="A101:A132" si="6">1+A100</f>
         <v>98</v>
@@ -38527,16 +38634,17 @@
       <c r="AQ101" s="13"/>
       <c r="AR101" s="13"/>
       <c r="AS101" s="13"/>
-      <c r="AT101" s="2"/>
+      <c r="AT101" s="13"/>
       <c r="AU101" s="2"/>
       <c r="AV101" s="2"/>
       <c r="AW101" s="2"/>
-      <c r="AX101" t="str">
+      <c r="AX101" s="2"/>
+      <c r="AY101" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1993, 1996, 1998, 1999, 2003, 2008, 2013, 2017, </v>
       </c>
     </row>
-    <row r="102" spans="1:50">
+    <row r="102" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A102" s="9">
         <f t="shared" si="6"/>
         <v>99</v>
@@ -38663,16 +38771,17 @@
       <c r="AQ102" s="13"/>
       <c r="AR102" s="13"/>
       <c r="AS102" s="13"/>
-      <c r="AT102" s="2"/>
+      <c r="AT102" s="13"/>
       <c r="AU102" s="2"/>
       <c r="AV102" s="2"/>
       <c r="AW102" s="2"/>
-      <c r="AX102" t="str">
+      <c r="AX102" s="2"/>
+      <c r="AY102" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50">
+    <row r="103" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A103" s="9">
         <f t="shared" si="6"/>
         <v>100</v>
@@ -38799,16 +38908,17 @@
       <c r="AQ103" s="13"/>
       <c r="AR103" s="13"/>
       <c r="AS103" s="13"/>
-      <c r="AT103" s="2"/>
+      <c r="AT103" s="13"/>
       <c r="AU103" s="2"/>
       <c r="AV103" s="2"/>
       <c r="AW103" s="2"/>
-      <c r="AX103" t="str">
+      <c r="AX103" s="2"/>
+      <c r="AY103" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2016, </v>
       </c>
     </row>
-    <row r="104" spans="1:50" s="23" customFormat="1">
+    <row r="104" spans="1:51" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="20">
         <f t="shared" si="6"/>
         <v>101</v>
@@ -38937,16 +39047,17 @@
       <c r="AQ104" s="19"/>
       <c r="AR104" s="19"/>
       <c r="AS104" s="19"/>
-      <c r="AT104" s="22"/>
+      <c r="AT104" s="19"/>
       <c r="AU104" s="22"/>
       <c r="AV104" s="22"/>
       <c r="AW104" s="22"/>
-      <c r="AX104" t="str">
+      <c r="AX104" s="22"/>
+      <c r="AY104" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2009, 2014, 2019, 2020, </v>
       </c>
     </row>
-    <row r="105" spans="1:50">
+    <row r="105" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A105" s="9">
         <f t="shared" si="6"/>
         <v>102</v>
@@ -39073,16 +39184,17 @@
       <c r="AQ105" s="13"/>
       <c r="AR105" s="13"/>
       <c r="AS105" s="13"/>
-      <c r="AT105" s="2"/>
+      <c r="AT105" s="13"/>
       <c r="AU105" s="2"/>
       <c r="AV105" s="2"/>
       <c r="AW105" s="2"/>
-      <c r="AX105" t="str">
+      <c r="AX105" s="2"/>
+      <c r="AY105" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1990, 2016, </v>
       </c>
     </row>
-    <row r="106" spans="1:50">
+    <row r="106" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A106" s="9">
         <f t="shared" si="6"/>
         <v>103</v>
@@ -39209,16 +39321,17 @@
       <c r="AQ106" s="13"/>
       <c r="AR106" s="13"/>
       <c r="AS106" s="13"/>
-      <c r="AT106" s="2"/>
+      <c r="AT106" s="13"/>
       <c r="AU106" s="2"/>
       <c r="AV106" s="2"/>
       <c r="AW106" s="2"/>
-      <c r="AX106" t="str">
+      <c r="AX106" s="2"/>
+      <c r="AY106" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2004, 2006, 2010, 2014, 2019, </v>
       </c>
     </row>
-    <row r="107" spans="1:50" s="23" customFormat="1">
+    <row r="107" spans="1:51" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="20">
         <f t="shared" si="6"/>
         <v>104</v>
@@ -39345,16 +39458,17 @@
       <c r="AQ107" s="19"/>
       <c r="AR107" s="19"/>
       <c r="AS107" s="19"/>
-      <c r="AT107" s="22"/>
+      <c r="AT107" s="19"/>
       <c r="AU107" s="22"/>
       <c r="AV107" s="22"/>
       <c r="AW107" s="22"/>
-      <c r="AX107" t="str">
+      <c r="AX107" s="22"/>
+      <c r="AY107" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2008, 2014, 2019, </v>
       </c>
     </row>
-    <row r="108" spans="1:50">
+    <row r="108" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A108" s="9">
         <f t="shared" si="6"/>
         <v>105</v>
@@ -39481,16 +39595,17 @@
       <c r="AQ108" s="13"/>
       <c r="AR108" s="13"/>
       <c r="AS108" s="13"/>
-      <c r="AT108" s="2"/>
+      <c r="AT108" s="13"/>
       <c r="AU108" s="2"/>
       <c r="AV108" s="2"/>
       <c r="AW108" s="2"/>
-      <c r="AX108" t="str">
+      <c r="AX108" s="2"/>
+      <c r="AY108" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50">
+    <row r="109" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A109" s="9">
         <f t="shared" si="6"/>
         <v>106</v>
@@ -39617,16 +39732,17 @@
       <c r="AQ109" s="13"/>
       <c r="AR109" s="13"/>
       <c r="AS109" s="13"/>
-      <c r="AT109" s="2"/>
+      <c r="AT109" s="13"/>
       <c r="AU109" s="2"/>
       <c r="AV109" s="2"/>
       <c r="AW109" s="2"/>
-      <c r="AX109" t="str">
+      <c r="AX109" s="2"/>
+      <c r="AY109" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1992, 2005, 2010, 2014, 2019, </v>
       </c>
     </row>
-    <row r="110" spans="1:50">
+    <row r="110" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A110" s="9">
         <f t="shared" si="6"/>
         <v>107</v>
@@ -39753,16 +39869,17 @@
       <c r="AQ110" s="13"/>
       <c r="AR110" s="13"/>
       <c r="AS110" s="13"/>
-      <c r="AT110" s="2"/>
+      <c r="AT110" s="13"/>
       <c r="AU110" s="2"/>
       <c r="AV110" s="2"/>
       <c r="AW110" s="2"/>
-      <c r="AX110" t="str">
+      <c r="AX110" s="2"/>
+      <c r="AY110" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1989, 1995, 2000, 2010, 2014, </v>
       </c>
     </row>
-    <row r="111" spans="1:50">
+    <row r="111" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A111" s="9">
         <f t="shared" si="6"/>
         <v>108</v>
@@ -39889,16 +40006,17 @@
       <c r="AQ111" s="13"/>
       <c r="AR111" s="13"/>
       <c r="AS111" s="13"/>
-      <c r="AT111" s="2"/>
+      <c r="AT111" s="13"/>
       <c r="AU111" s="2"/>
       <c r="AV111" s="2"/>
       <c r="AW111" s="2"/>
-      <c r="AX111" t="str">
+      <c r="AX111" s="2"/>
+      <c r="AY111" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1986, 1992, 1996, 1997, 1999, 2000, 2005, 2010, </v>
       </c>
     </row>
-    <row r="112" spans="1:50">
+    <row r="112" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A112" s="9">
         <f t="shared" si="6"/>
         <v>109</v>
@@ -40025,16 +40143,17 @@
       <c r="AQ112" s="13"/>
       <c r="AR112" s="13"/>
       <c r="AS112" s="13"/>
-      <c r="AT112" s="2"/>
+      <c r="AT112" s="13"/>
       <c r="AU112" s="2"/>
       <c r="AV112" s="2"/>
       <c r="AW112" s="2"/>
-      <c r="AX112" t="str">
+      <c r="AX112" s="2"/>
+      <c r="AY112" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2006, </v>
       </c>
     </row>
-    <row r="113" spans="1:50">
+    <row r="113" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A113" s="9">
         <f t="shared" si="6"/>
         <v>110</v>
@@ -40161,16 +40280,17 @@
       <c r="AQ113" s="13"/>
       <c r="AR113" s="13"/>
       <c r="AS113" s="13"/>
-      <c r="AT113" s="2"/>
+      <c r="AT113" s="13"/>
       <c r="AU113" s="2"/>
       <c r="AV113" s="2"/>
       <c r="AW113" s="2"/>
-      <c r="AX113" t="str">
+      <c r="AX113" s="2"/>
+      <c r="AY113" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1995, 2000, 2005, 2008, 2010, 2013, 2017, 2019, </v>
       </c>
     </row>
-    <row r="114" spans="1:50">
+    <row r="114" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A114" s="9">
         <f t="shared" si="6"/>
         <v>111</v>
@@ -40297,16 +40417,17 @@
       <c r="AQ114" s="13"/>
       <c r="AR114" s="13"/>
       <c r="AS114" s="13"/>
-      <c r="AT114" s="2"/>
+      <c r="AT114" s="13"/>
       <c r="AU114" s="2"/>
       <c r="AV114" s="2"/>
       <c r="AW114" s="2"/>
-      <c r="AX114" t="str">
+      <c r="AX114" s="2"/>
+      <c r="AY114" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1993, 1998, 2008, 2014, </v>
       </c>
     </row>
-    <row r="115" spans="1:50">
+    <row r="115" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A115" s="9">
         <f t="shared" si="6"/>
         <v>112</v>
@@ -40433,16 +40554,17 @@
       <c r="AQ115" s="13"/>
       <c r="AR115" s="13"/>
       <c r="AS115" s="13"/>
-      <c r="AT115" s="2"/>
+      <c r="AT115" s="13"/>
       <c r="AU115" s="2"/>
       <c r="AV115" s="2"/>
       <c r="AW115" s="2"/>
-      <c r="AX115" t="str">
+      <c r="AX115" s="2"/>
+      <c r="AY115" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2000, 2006, </v>
       </c>
     </row>
-    <row r="116" spans="1:50">
+    <row r="116" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A116" s="9">
         <f t="shared" si="6"/>
         <v>113</v>
@@ -40569,16 +40691,17 @@
       <c r="AQ116" s="13"/>
       <c r="AR116" s="13"/>
       <c r="AS116" s="13"/>
-      <c r="AT116" s="2"/>
+      <c r="AT116" s="13"/>
       <c r="AU116" s="2"/>
       <c r="AV116" s="2"/>
       <c r="AW116" s="2"/>
-      <c r="AX116" t="str">
+      <c r="AX116" s="2"/>
+      <c r="AY116" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2005, 2010, 2014, </v>
       </c>
     </row>
-    <row r="117" spans="1:50">
+    <row r="117" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A117" s="9">
         <f t="shared" si="6"/>
         <v>114</v>
@@ -40705,16 +40828,17 @@
       <c r="AQ117" s="13"/>
       <c r="AR117" s="13"/>
       <c r="AS117" s="13"/>
-      <c r="AT117" s="2"/>
+      <c r="AT117" s="13"/>
       <c r="AU117" s="2"/>
       <c r="AV117" s="2"/>
       <c r="AW117" s="2"/>
-      <c r="AX117" t="str">
+      <c r="AX117" s="2"/>
+      <c r="AY117" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2010, </v>
       </c>
     </row>
-    <row r="118" spans="1:50">
+    <row r="118" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A118" s="9">
         <f t="shared" si="6"/>
         <v>115</v>
@@ -40841,16 +40965,17 @@
       <c r="AQ118" s="13"/>
       <c r="AR118" s="13"/>
       <c r="AS118" s="13"/>
-      <c r="AT118" s="2"/>
+      <c r="AT118" s="13"/>
       <c r="AU118" s="2"/>
       <c r="AV118" s="2"/>
       <c r="AW118" s="2"/>
-      <c r="AX118" t="str">
+      <c r="AX118" s="2"/>
+      <c r="AY118" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1996, 2000, 2006, 2008, 2014, 2019, </v>
       </c>
     </row>
-    <row r="119" spans="1:50">
+    <row r="119" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A119" s="9">
         <f t="shared" si="6"/>
         <v>116</v>
@@ -40977,16 +41102,17 @@
       <c r="AQ119" s="13"/>
       <c r="AR119" s="13"/>
       <c r="AS119" s="13"/>
-      <c r="AT119" s="2"/>
+      <c r="AT119" s="13"/>
       <c r="AU119" s="2"/>
       <c r="AV119" s="2"/>
       <c r="AW119" s="2"/>
-      <c r="AX119" t="str">
+      <c r="AX119" s="2"/>
+      <c r="AY119" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1999, 2006, 2010, 2018, </v>
       </c>
     </row>
-    <row r="120" spans="1:50">
+    <row r="120" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A120" s="9">
         <f t="shared" si="6"/>
         <v>117</v>
@@ -41113,16 +41239,17 @@
       <c r="AQ120" s="13"/>
       <c r="AR120" s="13"/>
       <c r="AS120" s="13"/>
-      <c r="AT120" s="2"/>
+      <c r="AT120" s="13"/>
       <c r="AU120" s="2"/>
       <c r="AV120" s="2"/>
       <c r="AW120" s="2"/>
-      <c r="AX120" t="str">
+      <c r="AX120" s="2"/>
+      <c r="AY120" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1995, 2000, 2003, 2006, 2010, 2014, </v>
       </c>
     </row>
-    <row r="121" spans="1:50">
+    <row r="121" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A121" s="9">
         <f t="shared" si="6"/>
         <v>118</v>
@@ -41249,16 +41376,17 @@
       <c r="AQ121" s="13"/>
       <c r="AR121" s="13"/>
       <c r="AS121" s="13"/>
-      <c r="AT121" s="2"/>
+      <c r="AT121" s="13"/>
       <c r="AU121" s="2"/>
       <c r="AV121" s="2"/>
       <c r="AW121" s="2"/>
-      <c r="AX121" t="str">
+      <c r="AX121" s="2"/>
+      <c r="AY121" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:50">
+    <row r="122" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A122" s="9">
         <f t="shared" si="6"/>
         <v>119</v>
@@ -41385,16 +41513,17 @@
       <c r="AQ122" s="13"/>
       <c r="AR122" s="13"/>
       <c r="AS122" s="13"/>
-      <c r="AT122" s="2"/>
+      <c r="AT122" s="13"/>
       <c r="AU122" s="2"/>
       <c r="AV122" s="2"/>
       <c r="AW122" s="2"/>
-      <c r="AX122" t="str">
+      <c r="AX122" s="2"/>
+      <c r="AY122" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1995, 2000, 2006, </v>
       </c>
     </row>
-    <row r="123" spans="1:50">
+    <row r="123" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A123" s="9">
         <f t="shared" si="6"/>
         <v>120</v>
@@ -41521,16 +41650,17 @@
       <c r="AQ123" s="13"/>
       <c r="AR123" s="13"/>
       <c r="AS123" s="13"/>
-      <c r="AT123" s="2"/>
+      <c r="AT123" s="13"/>
       <c r="AU123" s="2"/>
       <c r="AV123" s="2"/>
       <c r="AW123" s="2"/>
-      <c r="AX123" t="str">
+      <c r="AX123" s="2"/>
+      <c r="AY123" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1997, 2000, 2003, 2004, 2010, 2014, 2019, </v>
       </c>
     </row>
-    <row r="124" spans="1:50">
+    <row r="124" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A124" s="9">
         <f t="shared" si="6"/>
         <v>121</v>
@@ -41657,16 +41787,17 @@
       <c r="AQ124" s="13"/>
       <c r="AR124" s="13"/>
       <c r="AS124" s="13"/>
-      <c r="AT124" s="2"/>
+      <c r="AT124" s="13"/>
       <c r="AU124" s="2"/>
       <c r="AV124" s="2"/>
       <c r="AW124" s="2"/>
-      <c r="AX124" t="str">
+      <c r="AX124" s="2"/>
+      <c r="AY124" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1988, 1996, 1998, 2000, 2006, 2010, 2013, 2017, </v>
       </c>
     </row>
-    <row r="125" spans="1:50">
+    <row r="125" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A125" s="9">
         <f t="shared" si="6"/>
         <v>122</v>
@@ -41793,16 +41924,17 @@
       <c r="AQ125" s="13"/>
       <c r="AR125" s="13"/>
       <c r="AS125" s="13"/>
-      <c r="AT125" s="2"/>
+      <c r="AT125" s="13"/>
       <c r="AU125" s="2"/>
       <c r="AV125" s="2"/>
       <c r="AW125" s="2"/>
-      <c r="AX125" t="str">
+      <c r="AX125" s="2"/>
+      <c r="AY125" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1987, 2005, 2012, 2015, 2019, </v>
       </c>
     </row>
-    <row r="126" spans="1:50">
+    <row r="126" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A126" s="9">
         <f t="shared" si="6"/>
         <v>123</v>
@@ -41929,16 +42061,17 @@
       <c r="AQ126" s="13"/>
       <c r="AR126" s="13"/>
       <c r="AS126" s="13"/>
-      <c r="AT126" s="2"/>
+      <c r="AT126" s="13"/>
       <c r="AU126" s="2"/>
       <c r="AV126" s="2"/>
       <c r="AW126" s="2"/>
-      <c r="AX126" t="str">
+      <c r="AX126" s="2"/>
+      <c r="AY126" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2000, 2005, 2012, 2017, </v>
       </c>
     </row>
-    <row r="127" spans="1:50">
+    <row r="127" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A127" s="9">
         <f t="shared" si="6"/>
         <v>124</v>
@@ -42065,16 +42198,17 @@
       <c r="AQ127" s="13"/>
       <c r="AR127" s="13"/>
       <c r="AS127" s="13"/>
-      <c r="AT127" s="2"/>
+      <c r="AT127" s="13"/>
       <c r="AU127" s="2"/>
       <c r="AV127" s="2"/>
       <c r="AW127" s="2"/>
-      <c r="AX127" t="str">
+      <c r="AX127" s="2"/>
+      <c r="AY127" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1996, 2000, 2006, 2015, 2019, </v>
       </c>
     </row>
-    <row r="128" spans="1:50">
+    <row r="128" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A128" s="9">
         <f t="shared" si="6"/>
         <v>125</v>
@@ -42201,16 +42335,17 @@
       <c r="AQ128" s="13"/>
       <c r="AR128" s="13"/>
       <c r="AS128" s="13"/>
-      <c r="AT128" s="2"/>
+      <c r="AT128" s="13"/>
       <c r="AU128" s="2"/>
       <c r="AV128" s="2"/>
       <c r="AW128" s="2"/>
-      <c r="AX128" t="str">
+      <c r="AX128" s="2"/>
+      <c r="AY128" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2002, 2009, 2016, </v>
       </c>
     </row>
-    <row r="129" spans="1:50">
+    <row r="129" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A129" s="9">
         <f t="shared" si="6"/>
         <v>126</v>
@@ -42337,16 +42472,17 @@
       <c r="AQ129" s="13"/>
       <c r="AR129" s="13"/>
       <c r="AS129" s="13"/>
-      <c r="AT129" s="2"/>
+      <c r="AT129" s="13"/>
       <c r="AU129" s="2"/>
       <c r="AV129" s="2"/>
       <c r="AW129" s="2"/>
-      <c r="AX129" t="str">
+      <c r="AX129" s="2"/>
+      <c r="AY129" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">2012, 2019, </v>
       </c>
     </row>
-    <row r="130" spans="1:50">
+    <row r="130" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A130" s="9">
         <f t="shared" si="6"/>
         <v>127</v>
@@ -42473,16 +42609,17 @@
       <c r="AQ130" s="13"/>
       <c r="AR130" s="13"/>
       <c r="AS130" s="13"/>
-      <c r="AT130" s="2"/>
+      <c r="AT130" s="13"/>
       <c r="AU130" s="2"/>
       <c r="AV130" s="2"/>
       <c r="AW130" s="2"/>
-      <c r="AX130" t="str">
+      <c r="AX130" s="2"/>
+      <c r="AY130" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1987, 2000, 2006, 2011, </v>
       </c>
     </row>
-    <row r="131" spans="1:50">
+    <row r="131" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A131" s="9">
         <f t="shared" si="6"/>
         <v>128</v>
@@ -42609,16 +42746,17 @@
       <c r="AQ131" s="13"/>
       <c r="AR131" s="13"/>
       <c r="AS131" s="13"/>
-      <c r="AT131" s="2"/>
+      <c r="AT131" s="13"/>
       <c r="AU131" s="2"/>
       <c r="AV131" s="2"/>
       <c r="AW131" s="2"/>
-      <c r="AX131" t="str">
+      <c r="AX131" s="2"/>
+      <c r="AY131" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1988, 2000, 2006, 2011, 2018, </v>
       </c>
     </row>
-    <row r="132" spans="1:50">
+    <row r="132" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A132" s="9">
         <f t="shared" si="6"/>
         <v>129</v>
@@ -42745,16 +42883,17 @@
       <c r="AQ132" s="13"/>
       <c r="AR132" s="13"/>
       <c r="AS132" s="13"/>
-      <c r="AT132" s="2"/>
+      <c r="AT132" s="13"/>
       <c r="AU132" s="2"/>
       <c r="AV132" s="2"/>
       <c r="AW132" s="2"/>
-      <c r="AX132" t="str">
+      <c r="AX132" s="2"/>
+      <c r="AY132" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve">1993, 1995, 1998, 2004, 2008, 2010, 2012, 2013, 2014, 2016, 2018, 2019, </v>
       </c>
     </row>
-    <row r="133" spans="1:50">
+    <row r="133" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A133" s="9">
         <f t="shared" ref="A133:A193" si="7">1+A132</f>
         <v>130</v>
@@ -42881,16 +43020,17 @@
       <c r="AQ133" s="13"/>
       <c r="AR133" s="13"/>
       <c r="AS133" s="13"/>
-      <c r="AT133" s="2"/>
+      <c r="AT133" s="13"/>
       <c r="AU133" s="2"/>
       <c r="AV133" s="2"/>
       <c r="AW133" s="2"/>
-      <c r="AX133" t="str">
-        <f t="shared" ref="AX133:AX193" si="8">+IF($F133=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G133=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H133=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I133=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J133=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K133=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L133=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M133=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N133=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O133=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P133=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q133=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R133=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S133=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T133=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U133=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V133=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W133=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X133=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y133=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z133=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA133=1,RIGHT(AA$3,4)&amp;", ","")&amp;IF($AB133=1,RIGHT(AB$3,4)&amp;", ","")&amp;IF($AC133=1,RIGHT(AC$3,4)&amp;", ","")&amp;IF($AD133=1,RIGHT(AD$3,4)&amp;", ","")&amp;IF($AE133=1,RIGHT(AE$3,4)&amp;", ","")&amp;IF($AF133=1,RIGHT(AF$3,4)&amp;", ","")&amp;IF($AG133=1,RIGHT(AG$3,4)&amp;", ","")&amp;IF($AH133=1,RIGHT(AH$3,4)&amp;", ","")&amp;IF($AI133=1,RIGHT(AI$3,4)&amp;", ","")&amp;IF($AJ133=1,RIGHT(AJ$3,4)&amp;", ","")&amp;IF($AK133=1,RIGHT(AK$3,4)&amp;", ","")&amp;IF($AL133=1,RIGHT(AL$3,4)&amp;", ","")&amp;IF($AM133=1,RIGHT(AM$3,4)&amp;", ","")&amp;IF($AN133=1,RIGHT(AN$3,4)&amp;", ","")&amp;IF($AO133=1,RIGHT(AO$3,4)&amp;", ","")&amp;IF($AP133=1,RIGHT(AP$3,4)&amp;", ","")&amp;IF($AQ133=1,RIGHT(AQ$3,4)&amp;", ","")&amp;IF($AR133=1,RIGHT(AR$3,4)&amp;", ","")&amp;IF($AS133=1,RIGHT(AS$3,4)&amp;", ","")</f>
+      <c r="AX133" s="2"/>
+      <c r="AY133" t="str">
+        <f t="shared" ref="AY133:AY193" si="8">+IF($F133=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G133=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H133=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I133=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J133=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K133=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L133=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M133=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N133=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O133=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P133=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q133=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R133=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S133=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T133=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U133=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V133=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W133=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X133=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y133=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z133=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA133=1,RIGHT(AA$3,4)&amp;", ","")&amp;IF($AB133=1,RIGHT(AB$3,4)&amp;", ","")&amp;IF($AC133=1,RIGHT(AC$3,4)&amp;", ","")&amp;IF($AD133=1,RIGHT(AD$3,4)&amp;", ","")&amp;IF($AE133=1,RIGHT(AE$3,4)&amp;", ","")&amp;IF($AF133=1,RIGHT(AF$3,4)&amp;", ","")&amp;IF($AG133=1,RIGHT(AG$3,4)&amp;", ","")&amp;IF($AH133=1,RIGHT(AH$3,4)&amp;", ","")&amp;IF($AI133=1,RIGHT(AI$3,4)&amp;", ","")&amp;IF($AJ133=1,RIGHT(AJ$3,4)&amp;", ","")&amp;IF($AK133=1,RIGHT(AK$3,4)&amp;", ","")&amp;IF($AL133=1,RIGHT(AL$3,4)&amp;", ","")&amp;IF($AM133=1,RIGHT(AM$3,4)&amp;", ","")&amp;IF($AN133=1,RIGHT(AN$3,4)&amp;", ","")&amp;IF($AO133=1,RIGHT(AO$3,4)&amp;", ","")&amp;IF($AP133=1,RIGHT(AP$3,4)&amp;", ","")&amp;IF($AQ133=1,RIGHT(AQ$3,4)&amp;", ","")&amp;IF($AR133=1,RIGHT(AR$3,4)&amp;", ","")&amp;IF($AS133=1,RIGHT(AS$3,4)&amp;", ","")&amp;IF($AT133=1,RIGHT(AT$3,4)&amp;", ","")</f>
         <v xml:space="preserve">2019, </v>
       </c>
     </row>
-    <row r="134" spans="1:50">
+    <row r="134" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A134" s="9">
         <f t="shared" si="7"/>
         <v>131</v>
@@ -43017,16 +43157,17 @@
       <c r="AQ134" s="13"/>
       <c r="AR134" s="13"/>
       <c r="AS134" s="13"/>
-      <c r="AT134" s="2"/>
+      <c r="AT134" s="13"/>
       <c r="AU134" s="2"/>
       <c r="AV134" s="2"/>
       <c r="AW134" s="2"/>
-      <c r="AX134" t="str">
+      <c r="AX134" s="2"/>
+      <c r="AY134" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1991, 1999, 2004, 2010, 2015, </v>
       </c>
     </row>
-    <row r="135" spans="1:50">
+    <row r="135" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A135" s="9">
         <f t="shared" si="7"/>
         <v>132</v>
@@ -43153,16 +43294,17 @@
       <c r="AQ135" s="13"/>
       <c r="AR135" s="13"/>
       <c r="AS135" s="13"/>
-      <c r="AT135" s="2"/>
+      <c r="AT135" s="13"/>
       <c r="AU135" s="2"/>
       <c r="AV135" s="2"/>
       <c r="AW135" s="2"/>
-      <c r="AX135" t="str">
+      <c r="AX135" s="2"/>
+      <c r="AY135" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1988, 1995, 2000, 2006, 2011, 2016, </v>
       </c>
     </row>
-    <row r="136" spans="1:50">
+    <row r="136" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A136" s="9">
         <f t="shared" si="7"/>
         <v>133</v>
@@ -43289,16 +43431,17 @@
       <c r="AQ136" s="13"/>
       <c r="AR136" s="13"/>
       <c r="AS136" s="13"/>
-      <c r="AT136" s="2"/>
+      <c r="AT136" s="13"/>
       <c r="AU136" s="2"/>
       <c r="AV136" s="2"/>
       <c r="AW136" s="2"/>
-      <c r="AX136" t="str">
+      <c r="AX136" s="2"/>
+      <c r="AY136" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2000, 2005, 2007, 2012, </v>
       </c>
     </row>
-    <row r="137" spans="1:50">
+    <row r="137" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A137" s="9">
         <f t="shared" si="7"/>
         <v>134</v>
@@ -43425,16 +43568,17 @@
       <c r="AQ137" s="13"/>
       <c r="AR137" s="13"/>
       <c r="AS137" s="13"/>
-      <c r="AT137" s="2"/>
+      <c r="AT137" s="13"/>
       <c r="AU137" s="2"/>
       <c r="AV137" s="2"/>
       <c r="AW137" s="2"/>
-      <c r="AX137" t="str">
+      <c r="AX137" s="2"/>
+      <c r="AY137" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2012, </v>
       </c>
     </row>
-    <row r="138" spans="1:50">
+    <row r="138" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A138" s="9">
         <f t="shared" si="7"/>
         <v>135</v>
@@ -43563,16 +43707,17 @@
       </c>
       <c r="AR138" s="13"/>
       <c r="AS138" s="13"/>
-      <c r="AT138" s="2"/>
+      <c r="AT138" s="13"/>
       <c r="AU138" s="2"/>
       <c r="AV138" s="2"/>
       <c r="AW138" s="2"/>
-      <c r="AX138" t="str">
+      <c r="AX138" s="2"/>
+      <c r="AY138" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1996, 2000, 2002, 2006, 2022, </v>
       </c>
     </row>
-    <row r="139" spans="1:50">
+    <row r="139" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A139" s="9">
         <f t="shared" si="7"/>
         <v>136</v>
@@ -43699,16 +43844,17 @@
       <c r="AQ139" s="13"/>
       <c r="AR139" s="13"/>
       <c r="AS139" s="13"/>
-      <c r="AT139" s="2"/>
+      <c r="AT139" s="13"/>
       <c r="AU139" s="2"/>
       <c r="AV139" s="2"/>
       <c r="AW139" s="2"/>
-      <c r="AX139" t="str">
+      <c r="AX139" s="2"/>
+      <c r="AY139" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2013, </v>
       </c>
     </row>
-    <row r="140" spans="1:50">
+    <row r="140" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A140" s="9">
         <f t="shared" si="7"/>
         <v>137</v>
@@ -43835,16 +43981,17 @@
       <c r="AQ140" s="13"/>
       <c r="AR140" s="13"/>
       <c r="AS140" s="13"/>
-      <c r="AT140" s="2"/>
+      <c r="AT140" s="13"/>
       <c r="AU140" s="2"/>
       <c r="AV140" s="2"/>
       <c r="AW140" s="2"/>
-      <c r="AX140" t="str">
+      <c r="AX140" s="2"/>
+      <c r="AY140" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2000, </v>
       </c>
     </row>
-    <row r="141" spans="1:50">
+    <row r="141" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A141" s="9">
         <f t="shared" si="7"/>
         <v>138</v>
@@ -43971,16 +44118,17 @@
       <c r="AQ141" s="13"/>
       <c r="AR141" s="13"/>
       <c r="AS141" s="13"/>
-      <c r="AT141" s="2"/>
+      <c r="AT141" s="13"/>
       <c r="AU141" s="2"/>
       <c r="AV141" s="2"/>
       <c r="AW141" s="2"/>
-      <c r="AX141" t="str">
+      <c r="AX141" s="2"/>
+      <c r="AY141" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1996, 1997, 2000, 2002, 2006, 2010, 2013, </v>
       </c>
     </row>
-    <row r="142" spans="1:50">
+    <row r="142" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A142" s="9">
         <f t="shared" si="7"/>
         <v>139</v>
@@ -44107,16 +44255,17 @@
       <c r="AQ142" s="13"/>
       <c r="AR142" s="13"/>
       <c r="AS142" s="13"/>
-      <c r="AT142" s="2"/>
+      <c r="AT142" s="13"/>
       <c r="AU142" s="2"/>
       <c r="AV142" s="2"/>
       <c r="AW142" s="2"/>
-      <c r="AX142" t="str">
+      <c r="AX142" s="2"/>
+      <c r="AY142" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2007, 2013, </v>
       </c>
     </row>
-    <row r="143" spans="1:50">
+    <row r="143" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A143" s="9">
         <f t="shared" si="7"/>
         <v>140</v>
@@ -44243,16 +44392,17 @@
       <c r="AQ143" s="13"/>
       <c r="AR143" s="13"/>
       <c r="AS143" s="13"/>
-      <c r="AT143" s="2"/>
+      <c r="AT143" s="13"/>
       <c r="AU143" s="2"/>
       <c r="AV143" s="2"/>
       <c r="AW143" s="2"/>
-      <c r="AX143" t="str">
+      <c r="AX143" s="2"/>
+      <c r="AY143" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2009, 2019, </v>
       </c>
     </row>
-    <row r="144" spans="1:50">
+    <row r="144" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A144" s="9">
         <f t="shared" si="7"/>
         <v>141</v>
@@ -44379,16 +44529,17 @@
       <c r="AQ144" s="13"/>
       <c r="AR144" s="13"/>
       <c r="AS144" s="13"/>
-      <c r="AT144" s="2"/>
+      <c r="AT144" s="13"/>
       <c r="AU144" s="2"/>
       <c r="AV144" s="2"/>
       <c r="AW144" s="2"/>
-      <c r="AX144" t="str">
+      <c r="AX144" s="2"/>
+      <c r="AY144" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2013, 2019, </v>
       </c>
     </row>
-    <row r="145" spans="1:50">
+    <row r="145" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A145" s="9">
         <f t="shared" si="7"/>
         <v>142</v>
@@ -44515,16 +44666,17 @@
       <c r="AQ145" s="13"/>
       <c r="AR145" s="13"/>
       <c r="AS145" s="13"/>
-      <c r="AT145" s="2"/>
+      <c r="AT145" s="13"/>
       <c r="AU145" s="2"/>
       <c r="AV145" s="2"/>
       <c r="AW145" s="2"/>
-      <c r="AX145" t="str">
+      <c r="AX145" s="2"/>
+      <c r="AY145" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1991, 1996, 1997, 2006, 2013, </v>
       </c>
     </row>
-    <row r="146" spans="1:50">
+    <row r="146" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A146" s="9">
         <f t="shared" si="7"/>
         <v>143</v>
@@ -44651,16 +44803,17 @@
       <c r="AQ146" s="13"/>
       <c r="AR146" s="13"/>
       <c r="AS146" s="13"/>
-      <c r="AT146" s="2"/>
+      <c r="AT146" s="13"/>
       <c r="AU146" s="2"/>
       <c r="AV146" s="2"/>
       <c r="AW146" s="2"/>
-      <c r="AX146" t="str">
+      <c r="AX146" s="2"/>
+      <c r="AY146" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1998, 2003, 2016, </v>
       </c>
     </row>
-    <row r="147" spans="1:50">
+    <row r="147" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A147" s="9">
         <f t="shared" si="7"/>
         <v>144</v>
@@ -44787,16 +44940,17 @@
       <c r="AQ147" s="13"/>
       <c r="AR147" s="13"/>
       <c r="AS147" s="13"/>
-      <c r="AT147" s="2"/>
+      <c r="AT147" s="13"/>
       <c r="AU147" s="2"/>
       <c r="AV147" s="2"/>
       <c r="AW147" s="2"/>
-      <c r="AX147" t="str">
+      <c r="AX147" s="2"/>
+      <c r="AY147" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1992, 1995, 1997, 1999, 2001, 2007, 2013, 2018, </v>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="17.45" customHeight="1">
+    <row r="148" spans="1:51" ht="17.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="9">
         <f t="shared" si="7"/>
         <v>145</v>
@@ -44923,16 +45077,17 @@
       <c r="AQ148" s="13"/>
       <c r="AR148" s="13"/>
       <c r="AS148" s="13"/>
-      <c r="AT148" s="2"/>
+      <c r="AT148" s="13"/>
       <c r="AU148" s="2"/>
       <c r="AV148" s="2"/>
       <c r="AW148" s="2"/>
-      <c r="AX148" t="str">
+      <c r="AX148" s="2"/>
+      <c r="AY148" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1989, 1994, 1999, 2005, 2009, 2010, 2014, 2015, 2019, </v>
       </c>
     </row>
-    <row r="149" spans="1:50">
+    <row r="149" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A149" s="9">
         <f t="shared" si="7"/>
         <v>146</v>
@@ -45060,15 +45215,16 @@
       <c r="AR149" s="24"/>
       <c r="AS149" s="24"/>
       <c r="AT149" s="24"/>
-      <c r="AU149" s="2"/>
+      <c r="AU149" s="24"/>
       <c r="AV149" s="2"/>
       <c r="AW149" s="2"/>
-      <c r="AX149" t="str">
+      <c r="AX149" s="2"/>
+      <c r="AY149" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2000, 2018, </v>
       </c>
     </row>
-    <row r="150" spans="1:50">
+    <row r="150" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A150" s="9">
         <f t="shared" si="7"/>
         <v>147</v>
@@ -45196,15 +45352,16 @@
       <c r="AR150" s="24"/>
       <c r="AS150" s="24"/>
       <c r="AT150" s="24"/>
-      <c r="AU150" s="2"/>
+      <c r="AU150" s="24"/>
       <c r="AV150" s="2"/>
       <c r="AW150" s="2"/>
-      <c r="AX150" t="str">
+      <c r="AX150" s="2"/>
+      <c r="AY150" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2012, </v>
       </c>
     </row>
-    <row r="151" spans="1:50">
+    <row r="151" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A151" s="9">
         <f t="shared" si="7"/>
         <v>148</v>
@@ -45331,20 +45488,21 @@
       <c r="AQ151" s="24"/>
       <c r="AR151" s="24"/>
       <c r="AS151" s="24"/>
-      <c r="AT151" s="25" t="s">
+      <c r="AT151" s="24"/>
+      <c r="AU151" s="25" t="s">
         <v>392</v>
       </c>
-      <c r="AU151" s="28" t="s">
+      <c r="AV151" s="28" t="s">
         <v>393</v>
       </c>
-      <c r="AV151" s="2"/>
       <c r="AW151" s="2"/>
-      <c r="AX151" t="str">
+      <c r="AX151" s="2"/>
+      <c r="AY151" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1993, 1996, 1999, 2002, 2008, 2014, 2019, </v>
       </c>
     </row>
-    <row r="152" spans="1:50">
+    <row r="152" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A152" s="9">
         <f t="shared" si="7"/>
         <v>149</v>
@@ -45471,18 +45629,19 @@
       <c r="AQ152" s="24"/>
       <c r="AR152" s="24"/>
       <c r="AS152" s="24"/>
-      <c r="AT152" s="25" t="s">
+      <c r="AT152" s="24"/>
+      <c r="AU152" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="AU152" s="2"/>
       <c r="AV152" s="2"/>
       <c r="AW152" s="2"/>
-      <c r="AX152" t="str">
+      <c r="AX152" s="2"/>
+      <c r="AY152" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2009, 2014, 2019, </v>
       </c>
     </row>
-    <row r="153" spans="1:50">
+    <row r="153" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A153" s="9">
         <f t="shared" si="7"/>
         <v>150</v>
@@ -45609,20 +45768,21 @@
       <c r="AQ153" s="24"/>
       <c r="AR153" s="24"/>
       <c r="AS153" s="24"/>
-      <c r="AT153" s="25" t="s">
+      <c r="AT153" s="24"/>
+      <c r="AU153" s="25" t="s">
         <v>397</v>
       </c>
-      <c r="AU153" s="2" t="s">
+      <c r="AV153" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="AV153" s="2"/>
       <c r="AW153" s="2"/>
-      <c r="AX153" t="str">
+      <c r="AX153" s="2"/>
+      <c r="AY153" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2009, 2014, 2019, </v>
       </c>
     </row>
-    <row r="154" spans="1:50">
+    <row r="154" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A154" s="9">
         <f t="shared" si="7"/>
         <v>151</v>
@@ -45749,18 +45909,19 @@
       <c r="AQ154" s="26"/>
       <c r="AR154" s="26"/>
       <c r="AS154" s="26"/>
-      <c r="AT154" s="32" t="s">
+      <c r="AT154" s="26"/>
+      <c r="AU154" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="AU154" s="22"/>
-      <c r="AV154" s="2"/>
+      <c r="AV154" s="22"/>
       <c r="AW154" s="2"/>
-      <c r="AX154" t="str">
+      <c r="AX154" s="2"/>
+      <c r="AY154" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2008, 2014, 2019, </v>
       </c>
     </row>
-    <row r="155" spans="1:50">
+    <row r="155" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A155" s="9">
         <f t="shared" si="7"/>
         <v>152</v>
@@ -45887,18 +46048,19 @@
       <c r="AQ155" s="24"/>
       <c r="AR155" s="24"/>
       <c r="AS155" s="24"/>
-      <c r="AT155" s="24" t="s">
+      <c r="AT155" s="24"/>
+      <c r="AU155" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="AU155" s="2"/>
       <c r="AV155" s="2"/>
       <c r="AW155" s="2"/>
-      <c r="AX155" t="str">
+      <c r="AX155" s="2"/>
+      <c r="AY155" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2014, 2019, </v>
       </c>
     </row>
-    <row r="156" spans="1:50">
+    <row r="156" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A156" s="9">
         <f t="shared" si="7"/>
         <v>153</v>
@@ -46026,15 +46188,16 @@
       <c r="AR156" s="24"/>
       <c r="AS156" s="24"/>
       <c r="AT156" s="24"/>
-      <c r="AU156" s="2"/>
+      <c r="AU156" s="24"/>
       <c r="AV156" s="2"/>
       <c r="AW156" s="2"/>
-      <c r="AX156" t="str">
+      <c r="AX156" s="2"/>
+      <c r="AY156" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1995, 2014, </v>
       </c>
     </row>
-    <row r="157" spans="1:50">
+    <row r="157" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A157" s="9">
         <f t="shared" si="7"/>
         <v>154</v>
@@ -46163,18 +46326,19 @@
         <v>1</v>
       </c>
       <c r="AS157" s="24"/>
-      <c r="AT157" s="25" t="s">
+      <c r="AT157" s="24"/>
+      <c r="AU157" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="AU157" s="2"/>
       <c r="AV157" s="2"/>
       <c r="AW157" s="2"/>
-      <c r="AX157" t="str">
+      <c r="AX157" s="2"/>
+      <c r="AY157" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2017, 2018, 2023, </v>
       </c>
     </row>
-    <row r="158" spans="1:50">
+    <row r="158" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A158" s="9">
         <f t="shared" si="7"/>
         <v>155</v>
@@ -46301,18 +46465,19 @@
       <c r="AQ158" s="24"/>
       <c r="AR158" s="24"/>
       <c r="AS158" s="24"/>
-      <c r="AT158" s="25" t="s">
+      <c r="AT158" s="24"/>
+      <c r="AU158" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="AU158" s="2"/>
       <c r="AV158" s="2"/>
       <c r="AW158" s="2"/>
-      <c r="AX158" t="str">
+      <c r="AX158" s="2"/>
+      <c r="AY158" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2009, 2014, 2019, </v>
       </c>
     </row>
-    <row r="159" spans="1:50">
+    <row r="159" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A159" s="9">
         <f t="shared" si="7"/>
         <v>156</v>
@@ -46439,18 +46604,19 @@
       <c r="AQ159" s="2"/>
       <c r="AR159" s="2"/>
       <c r="AS159" s="2"/>
-      <c r="AT159" s="2" t="s">
+      <c r="AT159" s="2"/>
+      <c r="AU159" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="AU159" s="2"/>
       <c r="AV159" s="2"/>
       <c r="AW159" s="2"/>
-      <c r="AX159" t="str">
+      <c r="AX159" s="2"/>
+      <c r="AY159" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2019, </v>
       </c>
     </row>
-    <row r="160" spans="1:50">
+    <row r="160" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A160" s="9">
         <f t="shared" si="7"/>
         <v>157</v>
@@ -46581,12 +46747,13 @@
       <c r="AU160" s="2"/>
       <c r="AV160" s="2"/>
       <c r="AW160" s="2"/>
-      <c r="AX160" t="str">
+      <c r="AX160" s="2"/>
+      <c r="AY160" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50">
+    <row r="161" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A161" s="9">
         <f t="shared" si="7"/>
         <v>158</v>
@@ -46717,20 +46884,21 @@
       <c r="AS161" s="2">
         <v>1</v>
       </c>
-      <c r="AT161" s="28" t="s">
+      <c r="AT161" s="2"/>
+      <c r="AU161" s="28" t="s">
         <v>411</v>
       </c>
-      <c r="AU161" s="2" t="s">
+      <c r="AV161" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="AV161" s="2"/>
       <c r="AW161" s="2"/>
-      <c r="AX161" t="str">
+      <c r="AX161" s="2"/>
+      <c r="AY161" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1989, 1995, 2001, 2004, 2007, 2011, 2014, 2017, 2022, 2024, </v>
       </c>
     </row>
-    <row r="162" spans="1:50">
+    <row r="162" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A162" s="9">
         <f t="shared" si="7"/>
         <v>159</v>
@@ -46857,20 +47025,21 @@
       <c r="AQ162" s="2"/>
       <c r="AR162" s="2"/>
       <c r="AS162" s="2"/>
-      <c r="AT162" s="28" t="s">
+      <c r="AT162" s="2"/>
+      <c r="AU162" s="28" t="s">
         <v>414</v>
       </c>
-      <c r="AU162" s="2" t="s">
+      <c r="AV162" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="AV162" s="2"/>
       <c r="AW162" s="2"/>
-      <c r="AX162" t="str">
+      <c r="AX162" s="2"/>
+      <c r="AY162" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2006, 2014, 2019, </v>
       </c>
     </row>
-    <row r="163" spans="1:50">
+    <row r="163" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A163" s="9">
         <f t="shared" si="7"/>
         <v>160</v>
@@ -46999,20 +47168,21 @@
       <c r="AS163" s="2">
         <v>1</v>
       </c>
-      <c r="AT163" s="28" t="s">
+      <c r="AT163" s="2"/>
+      <c r="AU163" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="AU163" s="29" t="s">
+      <c r="AV163" s="29" t="s">
         <v>417</v>
       </c>
-      <c r="AV163" s="2"/>
       <c r="AW163" s="2"/>
-      <c r="AX163" t="str">
+      <c r="AX163" s="2"/>
+      <c r="AY163" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2008, 2013, 2019, 2024, </v>
       </c>
     </row>
-    <row r="164" spans="1:50">
+    <row r="164" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A164" s="9">
         <f t="shared" si="7"/>
         <v>161</v>
@@ -47143,12 +47313,13 @@
       <c r="AU164" s="2"/>
       <c r="AV164" s="2"/>
       <c r="AW164" s="2"/>
-      <c r="AX164" t="str">
+      <c r="AX164" s="2"/>
+      <c r="AY164" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:50">
+    <row r="165" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A165" s="9">
         <f t="shared" si="7"/>
         <v>162</v>
@@ -47279,12 +47450,13 @@
       <c r="AU165" s="2"/>
       <c r="AV165" s="2"/>
       <c r="AW165" s="2"/>
-      <c r="AX165" t="str">
+      <c r="AX165" s="2"/>
+      <c r="AY165" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50">
+    <row r="166" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A166" s="9">
         <f t="shared" si="7"/>
         <v>163</v>
@@ -47421,20 +47593,23 @@
       <c r="AS166" s="2">
         <v>1</v>
       </c>
-      <c r="AT166" s="28" t="s">
+      <c r="AT166" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU166" s="28" t="s">
         <v>421</v>
       </c>
-      <c r="AU166" s="28" t="s">
+      <c r="AV166" s="28" t="s">
         <v>422</v>
       </c>
-      <c r="AV166" s="2"/>
       <c r="AW166" s="2"/>
-      <c r="AX166" t="str">
+      <c r="AX166" s="2"/>
+      <c r="AY166" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">1994, 1996, 1998, 2000, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
+        <v xml:space="preserve">1994, 1996, 1998, 2000, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
       </c>
     </row>
-    <row r="167" spans="1:50">
+    <row r="167" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A167" s="9">
         <f t="shared" si="7"/>
         <v>164</v>
@@ -47561,18 +47736,19 @@
       <c r="AQ167" s="2"/>
       <c r="AR167" s="2"/>
       <c r="AS167" s="2"/>
-      <c r="AT167" s="28" t="s">
+      <c r="AT167" s="2"/>
+      <c r="AU167" s="28" t="s">
         <v>424</v>
       </c>
-      <c r="AU167" s="2"/>
       <c r="AV167" s="2"/>
       <c r="AW167" s="2"/>
-      <c r="AX167" t="str">
+      <c r="AX167" s="2"/>
+      <c r="AY167" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1992, 1997, 2002, 2007, 2012, 2017, 2019, </v>
       </c>
     </row>
-    <row r="168" spans="1:50">
+    <row r="168" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A168" s="9">
         <f t="shared" si="7"/>
         <v>165</v>
@@ -47699,18 +47875,19 @@
       <c r="AQ168" s="2"/>
       <c r="AR168" s="2"/>
       <c r="AS168" s="2"/>
-      <c r="AT168" s="28" t="s">
+      <c r="AT168" s="2"/>
+      <c r="AU168" s="28" t="s">
         <v>426</v>
       </c>
-      <c r="AU168" s="2"/>
       <c r="AV168" s="2"/>
       <c r="AW168" s="2"/>
-      <c r="AX168" t="str">
+      <c r="AX168" s="2"/>
+      <c r="AY168" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2008, 2014, 2019, </v>
       </c>
     </row>
-    <row r="169" spans="1:50">
+    <row r="169" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A169" s="9">
         <f t="shared" si="7"/>
         <v>166</v>
@@ -47839,18 +48016,19 @@
       <c r="AQ169" s="2"/>
       <c r="AR169" s="2"/>
       <c r="AS169" s="2"/>
-      <c r="AT169" s="28" t="s">
+      <c r="AT169" s="2"/>
+      <c r="AU169" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="AU169" s="2"/>
       <c r="AV169" s="2"/>
       <c r="AW169" s="2"/>
-      <c r="AX169" t="str">
+      <c r="AX169" s="2"/>
+      <c r="AY169" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2009, 2015, 2019, 2020, </v>
       </c>
     </row>
-    <row r="170" spans="1:50">
+    <row r="170" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A170" s="9">
         <f t="shared" si="7"/>
         <v>167</v>
@@ -47977,18 +48155,19 @@
       <c r="AQ170" s="2"/>
       <c r="AR170" s="2"/>
       <c r="AS170" s="2"/>
-      <c r="AT170" s="28" t="s">
+      <c r="AT170" s="2"/>
+      <c r="AU170" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="AU170" s="2"/>
       <c r="AV170" s="2"/>
       <c r="AW170" s="2"/>
-      <c r="AX170" t="str">
+      <c r="AX170" s="2"/>
+      <c r="AY170" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2015, 2019, </v>
       </c>
     </row>
-    <row r="171" spans="1:50">
+    <row r="171" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A171" s="9">
         <f t="shared" si="7"/>
         <v>168</v>
@@ -48115,22 +48294,23 @@
       <c r="AQ171" s="2"/>
       <c r="AR171" s="2"/>
       <c r="AS171" s="2"/>
-      <c r="AT171" s="28" t="s">
+      <c r="AT171" s="2"/>
+      <c r="AU171" s="28" t="s">
         <v>430</v>
       </c>
-      <c r="AU171" s="30" t="s">
+      <c r="AV171" s="30" t="s">
         <v>431</v>
       </c>
-      <c r="AV171" s="2" t="s">
+      <c r="AW171" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="AW171" s="2"/>
-      <c r="AX171" t="str">
+      <c r="AX171" s="2"/>
+      <c r="AY171" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1993, 1995, 1997, 2001, 2003, 2006, 2009, 2011, 2014, 2017, 2019, </v>
       </c>
     </row>
-    <row r="172" spans="1:50">
+    <row r="172" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A172" s="9">
         <f>1+A171</f>
         <v>169</v>
@@ -48259,24 +48439,25 @@
       <c r="AS172" s="2">
         <v>1</v>
       </c>
-      <c r="AT172" s="28" t="s">
+      <c r="AT172" s="2"/>
+      <c r="AU172" s="28" t="s">
         <v>434</v>
       </c>
-      <c r="AU172" s="2" t="s">
+      <c r="AV172" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="AV172" s="2" t="s">
+      <c r="AW172" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="AW172" s="2" t="s">
+      <c r="AX172" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="AX172" t="str">
+      <c r="AY172" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1996, 2006, 2014, 2019, 2024, </v>
       </c>
     </row>
-    <row r="173" spans="1:50">
+    <row r="173" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A173" s="9">
         <f t="shared" si="7"/>
         <v>170</v>
@@ -48403,18 +48584,19 @@
       <c r="AQ173" s="2"/>
       <c r="AR173" s="2"/>
       <c r="AS173" s="2"/>
-      <c r="AT173" s="28" t="s">
+      <c r="AT173" s="2"/>
+      <c r="AU173" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="AU173" s="2"/>
       <c r="AV173" s="2"/>
       <c r="AW173" s="2"/>
-      <c r="AX173" t="str">
+      <c r="AX173" s="2"/>
+      <c r="AY173" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2014, 2019, </v>
       </c>
     </row>
-    <row r="174" spans="1:50">
+    <row r="174" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A174" s="9">
         <f t="shared" si="7"/>
         <v>171</v>
@@ -48543,20 +48725,21 @@
       <c r="AS174" s="2">
         <v>1</v>
       </c>
-      <c r="AT174" s="28" t="s">
+      <c r="AT174" s="2"/>
+      <c r="AU174" s="28" t="s">
         <v>439</v>
       </c>
-      <c r="AU174" s="28" t="s">
+      <c r="AV174" s="28" t="s">
         <v>440</v>
       </c>
-      <c r="AV174" s="2"/>
       <c r="AW174" s="2"/>
-      <c r="AX174" t="str">
+      <c r="AX174" s="2"/>
+      <c r="AY174" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2003, 2008, 2014, 2019, 2024, </v>
       </c>
     </row>
-    <row r="175" spans="1:50">
+    <row r="175" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A175" s="9">
         <f t="shared" si="7"/>
         <v>172</v>
@@ -48685,20 +48868,21 @@
       <c r="AS175" s="2">
         <v>1</v>
       </c>
-      <c r="AT175" s="29" t="s">
+      <c r="AT175" s="2"/>
+      <c r="AU175" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="AU175" s="29" t="s">
+      <c r="AV175" s="29" t="s">
         <v>442</v>
       </c>
-      <c r="AV175" s="2"/>
       <c r="AW175" s="2"/>
-      <c r="AX175" t="str">
+      <c r="AX175" s="2"/>
+      <c r="AY175" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2013, 2024, </v>
       </c>
     </row>
-    <row r="176" spans="1:50">
+    <row r="176" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A176" s="9">
         <f t="shared" si="7"/>
         <v>173</v>
@@ -48825,22 +49009,23 @@
       <c r="AQ176" s="2"/>
       <c r="AR176" s="2"/>
       <c r="AS176" s="2"/>
-      <c r="AT176" s="28" t="s">
+      <c r="AT176" s="2"/>
+      <c r="AU176" s="28" t="s">
         <v>444</v>
       </c>
-      <c r="AU176" s="2" t="s">
+      <c r="AV176" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="AV176" s="2" t="s">
+      <c r="AW176" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="AW176" s="2"/>
-      <c r="AX176" t="str">
+      <c r="AX176" s="2"/>
+      <c r="AY176" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2015, 2019, </v>
       </c>
     </row>
-    <row r="177" spans="1:50">
+    <row r="177" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A177" s="9">
         <f t="shared" si="7"/>
         <v>174</v>
@@ -48967,20 +49152,21 @@
       <c r="AQ177" s="2"/>
       <c r="AR177" s="2"/>
       <c r="AS177" s="2"/>
-      <c r="AT177" s="28" t="s">
+      <c r="AT177" s="2"/>
+      <c r="AU177" s="28" t="s">
         <v>448</v>
       </c>
-      <c r="AU177" s="2" t="s">
+      <c r="AV177" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="AV177" s="2"/>
       <c r="AW177" s="2"/>
-      <c r="AX177" t="str">
+      <c r="AX177" s="2"/>
+      <c r="AY177" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2015, 2019, </v>
       </c>
     </row>
-    <row r="178" spans="1:50">
+    <row r="178" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A178" s="9">
         <f t="shared" si="7"/>
         <v>175</v>
@@ -49109,24 +49295,25 @@
       <c r="AQ178" s="2"/>
       <c r="AR178" s="2"/>
       <c r="AS178" s="2"/>
-      <c r="AT178" s="29" t="s">
+      <c r="AT178" s="2"/>
+      <c r="AU178" s="29" t="s">
         <v>451</v>
       </c>
-      <c r="AU178" s="2" t="s">
+      <c r="AV178" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="AV178" s="2" t="s">
+      <c r="AW178" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="AW178" s="28" t="s">
+      <c r="AX178" s="28" t="s">
         <v>454</v>
       </c>
-      <c r="AX178" t="str">
+      <c r="AY178" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1995, 2009, 2015, 2017, 2019, 2020, </v>
       </c>
     </row>
-    <row r="179" spans="1:50">
+    <row r="179" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A179" s="9">
         <f t="shared" si="7"/>
         <v>176</v>
@@ -49255,20 +49442,21 @@
       <c r="AS179" s="2">
         <v>1</v>
       </c>
-      <c r="AT179" s="28" t="s">
+      <c r="AT179" s="2"/>
+      <c r="AU179" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="AU179" s="28" t="s">
+      <c r="AV179" s="28" t="s">
         <v>457</v>
       </c>
-      <c r="AV179" s="2"/>
       <c r="AW179" s="2"/>
-      <c r="AX179" t="str">
+      <c r="AX179" s="2"/>
+      <c r="AY179" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1994, 2000, 2012, 2015, 2019, 2024, </v>
       </c>
     </row>
-    <row r="180" spans="1:50">
+    <row r="180" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A180" s="9">
         <f t="shared" si="7"/>
         <v>177</v>
@@ -49388,31 +49576,36 @@
         <v>0</v>
       </c>
       <c r="AN180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO180" s="2"/>
       <c r="AP180" s="2"/>
-      <c r="AQ180" s="2"/>
+      <c r="AQ180" s="2">
+        <v>1</v>
+      </c>
       <c r="AR180" s="2"/>
       <c r="AS180" s="2"/>
-      <c r="AT180" s="28" t="s">
+      <c r="AT180" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU180" s="28" t="s">
         <v>459</v>
       </c>
-      <c r="AU180" s="29" t="s">
+      <c r="AV180" s="29" t="s">
         <v>460</v>
       </c>
-      <c r="AV180" s="28" t="s">
+      <c r="AW180" s="28" t="s">
         <v>461</v>
       </c>
-      <c r="AW180" s="28" t="s">
+      <c r="AX180" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="AX180" t="str">
+      <c r="AY180" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">2001, 2004, 2007, 2010, 2013, 2016, </v>
+        <v xml:space="preserve">2001, 2004, 2007, 2010, 2013, 2016, 2019, 2022, 2025, </v>
       </c>
     </row>
-    <row r="181" spans="1:50">
+    <row r="181" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A181" s="9">
         <f t="shared" si="7"/>
         <v>178</v>
@@ -49547,20 +49740,21 @@
         <v>1</v>
       </c>
       <c r="AS181" s="2"/>
-      <c r="AT181" s="28" t="s">
+      <c r="AT181" s="2"/>
+      <c r="AU181" s="28" t="s">
         <v>464</v>
       </c>
-      <c r="AU181" s="2"/>
-      <c r="AV181" s="28" t="s">
+      <c r="AV181" s="2"/>
+      <c r="AW181" s="28" t="s">
         <v>465</v>
       </c>
-      <c r="AW181" s="2"/>
-      <c r="AX181" t="str">
+      <c r="AX181" s="2"/>
+      <c r="AY181" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1998, 2001, 2005, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2020, 2021, 2022, 2023, </v>
       </c>
     </row>
-    <row r="182" spans="1:50">
+    <row r="182" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A182" s="9">
         <f t="shared" si="7"/>
         <v>179</v>
@@ -49687,18 +49881,19 @@
       <c r="AQ182" s="2"/>
       <c r="AR182" s="2"/>
       <c r="AS182" s="2"/>
-      <c r="AT182" s="2" t="s">
+      <c r="AT182" s="2"/>
+      <c r="AU182" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="AU182" s="2"/>
       <c r="AV182" s="2"/>
       <c r="AW182" s="2"/>
-      <c r="AX182" t="str">
+      <c r="AX182" s="2"/>
+      <c r="AY182" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50">
+    <row r="183" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A183" s="9">
         <f t="shared" si="7"/>
         <v>180</v>
@@ -49827,18 +50022,19 @@
       <c r="AS183" s="2">
         <v>1</v>
       </c>
-      <c r="AT183" s="28" t="s">
+      <c r="AT183" s="2"/>
+      <c r="AU183" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="AU183" s="28"/>
-      <c r="AV183" s="2"/>
+      <c r="AV183" s="28"/>
       <c r="AW183" s="2"/>
-      <c r="AX183" t="str">
+      <c r="AX183" s="2"/>
+      <c r="AY183" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2014, 2019, 2024, </v>
       </c>
     </row>
-    <row r="184" spans="1:50">
+    <row r="184" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A184" s="9">
         <f t="shared" si="7"/>
         <v>181</v>
@@ -49965,18 +50161,19 @@
       <c r="AQ184" s="2"/>
       <c r="AR184" s="2"/>
       <c r="AS184" s="2"/>
-      <c r="AT184" s="2" t="s">
+      <c r="AT184" s="2"/>
+      <c r="AU184" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="AU184" s="2"/>
       <c r="AV184" s="2"/>
       <c r="AW184" s="2"/>
-      <c r="AX184" t="str">
+      <c r="AX184" s="2"/>
+      <c r="AY184" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2008, 2014, 2019, </v>
       </c>
     </row>
-    <row r="185" spans="1:50">
+    <row r="185" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A185" s="9">
         <f t="shared" si="7"/>
         <v>182</v>
@@ -50105,20 +50302,21 @@
       <c r="AS185" s="2">
         <v>1</v>
       </c>
-      <c r="AT185" s="28" t="s">
+      <c r="AT185" s="2"/>
+      <c r="AU185" s="28" t="s">
         <v>471</v>
       </c>
-      <c r="AU185" s="2" t="s">
+      <c r="AV185" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="AV185" s="2"/>
       <c r="AW185" s="2"/>
-      <c r="AX185" t="str">
+      <c r="AX185" s="2"/>
+      <c r="AY185" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1985, 1986, 1987, 1988, 1989, 1990, 1991, 1992, 1993, 1994, 1995, 1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2024, </v>
       </c>
     </row>
-    <row r="186" spans="1:50">
+    <row r="186" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A186" s="9">
         <f t="shared" si="7"/>
         <v>183</v>
@@ -50247,22 +50445,23 @@
       <c r="AQ186" s="2"/>
       <c r="AR186" s="2"/>
       <c r="AS186" s="2"/>
-      <c r="AT186" s="28" t="s">
+      <c r="AT186" s="2"/>
+      <c r="AU186" s="28" t="s">
         <v>474</v>
       </c>
-      <c r="AU186" s="28" t="s">
+      <c r="AV186" s="28" t="s">
         <v>475</v>
       </c>
-      <c r="AV186" s="2" t="s">
+      <c r="AW186" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="AW186" s="2"/>
-      <c r="AX186" t="str">
+      <c r="AX186" s="2"/>
+      <c r="AY186" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1998, 2002, 2005, 2008, 2012, 2015, 2019, 2021, </v>
       </c>
     </row>
-    <row r="187" spans="1:50">
+    <row r="187" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A187" s="9">
         <f t="shared" si="7"/>
         <v>184</v>
@@ -50396,18 +50595,21 @@
       <c r="AS187" s="2">
         <v>1</v>
       </c>
-      <c r="AT187" s="2" t="s">
+      <c r="AT187" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU187" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="AU187" s="2"/>
       <c r="AV187" s="2"/>
       <c r="AW187" s="2"/>
-      <c r="AX187" t="str">
+      <c r="AX187" s="2"/>
+      <c r="AY187" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">2020, 2022, 2023, 2024, </v>
+        <v xml:space="preserve">2020, 2022, 2023, 2024, 2025, </v>
       </c>
     </row>
-    <row r="188" spans="1:50">
+    <row r="188" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A188" s="9">
         <f t="shared" si="7"/>
         <v>185</v>
@@ -50536,20 +50738,21 @@
       <c r="AS188" s="2">
         <v>1</v>
       </c>
-      <c r="AT188" s="28" t="s">
+      <c r="AT188" s="2"/>
+      <c r="AU188" s="28" t="s">
         <v>480</v>
       </c>
-      <c r="AU188" s="28" t="s">
+      <c r="AV188" s="28" t="s">
         <v>481</v>
       </c>
-      <c r="AV188" s="2"/>
       <c r="AW188" s="2"/>
-      <c r="AX188" t="str">
+      <c r="AX188" s="2"/>
+      <c r="AY188" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2005, 2014, 2019, 2024, </v>
       </c>
     </row>
-    <row r="189" spans="1:50">
+    <row r="189" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A189" s="9">
         <f t="shared" si="7"/>
         <v>186</v>
@@ -50676,18 +50879,19 @@
       <c r="AQ189" s="2"/>
       <c r="AR189" s="2"/>
       <c r="AS189" s="2"/>
-      <c r="AT189" s="2" t="s">
+      <c r="AT189" s="2"/>
+      <c r="AU189" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="AU189" s="2"/>
       <c r="AV189" s="2"/>
       <c r="AW189" s="2"/>
-      <c r="AX189" t="str">
+      <c r="AX189" s="2"/>
+      <c r="AY189" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2012, </v>
       </c>
     </row>
-    <row r="190" spans="1:50">
+    <row r="190" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A190" s="9">
         <f t="shared" si="7"/>
         <v>187</v>
@@ -50816,22 +51020,23 @@
       <c r="AQ190" s="2"/>
       <c r="AR190" s="2"/>
       <c r="AS190" s="2"/>
-      <c r="AT190" s="2" t="s">
+      <c r="AT190" s="2"/>
+      <c r="AU190" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="AU190" s="2" t="s">
+      <c r="AV190" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="AV190" s="2" t="s">
+      <c r="AW190" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="AW190" s="2"/>
-      <c r="AX190" t="str">
+      <c r="AX190" s="2"/>
+      <c r="AY190" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">1992, 1998, 2001, 2004, 2007, 2010, 2013, 2016, 2020, </v>
       </c>
     </row>
-    <row r="191" spans="1:50">
+    <row r="191" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A191" s="9">
         <f t="shared" si="7"/>
         <v>188</v>
@@ -50958,18 +51163,19 @@
       <c r="AQ191" s="2"/>
       <c r="AR191" s="2"/>
       <c r="AS191" s="2"/>
-      <c r="AT191" s="28" t="s">
+      <c r="AT191" s="2"/>
+      <c r="AU191" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="AU191" s="2"/>
       <c r="AV191" s="2"/>
       <c r="AW191" s="2"/>
-      <c r="AX191" t="str">
+      <c r="AX191" s="2"/>
+      <c r="AY191" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2007, 2014, 2019, </v>
       </c>
     </row>
-    <row r="192" spans="1:50">
+    <row r="192" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A192" s="9">
         <f t="shared" si="7"/>
         <v>189</v>
@@ -51096,18 +51302,19 @@
       <c r="AQ192" s="2"/>
       <c r="AR192" s="2"/>
       <c r="AS192" s="2"/>
-      <c r="AT192" s="28" t="s">
+      <c r="AT192" s="2"/>
+      <c r="AU192" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="AU192" s="29"/>
-      <c r="AV192" s="2"/>
+      <c r="AV192" s="29"/>
       <c r="AW192" s="2"/>
-      <c r="AX192" t="str">
+      <c r="AX192" s="2"/>
+      <c r="AY192" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">2014, 2019, </v>
       </c>
     </row>
-    <row r="193" spans="1:50">
+    <row r="193" spans="1:51" x14ac:dyDescent="0.2">
       <c r="A193" s="9">
         <f t="shared" si="7"/>
         <v>190</v>
@@ -51244,17 +51451,20 @@
       <c r="AS193" s="2">
         <v>1</v>
       </c>
-      <c r="AT193" s="28" t="s">
+      <c r="AT193" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU193" s="28" t="s">
         <v>491</v>
       </c>
-      <c r="AU193" s="28" t="s">
+      <c r="AV193" s="28" t="s">
         <v>492</v>
       </c>
-      <c r="AV193" s="2"/>
       <c r="AW193" s="2"/>
-      <c r="AX193" t="str">
-        <f>+IF($F193=1,RIGHT(F$3,4)&amp;", ","")&amp;IF($G193=1,RIGHT(G$3,4)&amp;", ","")&amp;IF($H193=1,RIGHT(H$3,4)&amp;", ","")&amp;IF($I193=1,RIGHT(I$3,4)&amp;", ","")&amp;IF($J193=1,RIGHT(J$3,4)&amp;", ","")&amp;IF($K193=1,RIGHT(K$3,4)&amp;", ","")&amp;IF($L193=1,RIGHT(L$3,4)&amp;", ","")&amp;IF($M193=1,RIGHT(M$3,4)&amp;", ","")&amp;IF($N193=1,RIGHT(N$3,4)&amp;", ","")&amp;IF($O193=1,RIGHT(O$3,4)&amp;", ","")&amp;IF($P193=1,RIGHT(P$3,4)&amp;", ","")&amp;IF($Q193=1,RIGHT(Q$3,4)&amp;", ","")&amp;IF($R193=1,RIGHT(R$3,4)&amp;", ","")&amp;IF($S193=1,RIGHT(S$3,4)&amp;", ","")&amp;IF($T193=1,RIGHT(T$3,4)&amp;", ","")&amp;IF($U193=1,RIGHT(U$3,4)&amp;", ","")&amp;IF($V193=1,RIGHT(V$3,4)&amp;", ","")&amp;IF($W193=1,RIGHT(W$3,4)&amp;", ","")&amp;IF($X193=1,RIGHT(X$3,4)&amp;", ","")&amp;IF($Y193=1,RIGHT(Y$3,4)&amp;", ","")&amp;IF($Z193=1,RIGHT(Z$3,4)&amp;", ","")&amp;IF($AA193=1,RIGHT(AA$3,4)&amp;", ","")&amp;IF($AB193=1,RIGHT(AB$3,4)&amp;", ","")&amp;IF($AC193=1,RIGHT(AC$3,4)&amp;", ","")&amp;IF($AD193=1,RIGHT(AD$3,4)&amp;", ","")&amp;IF($AE193=1,RIGHT(AE$3,4)&amp;", ","")&amp;IF($AF193=1,RIGHT(AF$3,4)&amp;", ","")&amp;IF($AG193=1,RIGHT(AG$3,4)&amp;", ","")&amp;IF($AH193=1,RIGHT(AH$3,4)&amp;", ","")&amp;IF($AI193=1,RIGHT(AI$3,4)&amp;", ","")&amp;IF($AJ193=1,RIGHT(AJ$3,4)&amp;", ","")&amp;IF($AK193=1,RIGHT(AK$3,4)&amp;", ","")&amp;IF($AL193=1,RIGHT(AL$3,4)&amp;", ","")&amp;IF($AM193=1,RIGHT(AM$3,4)&amp;", ","")&amp;IF($AN193=1,RIGHT(AN$3,4)&amp;", ","")&amp;IF($AO193=1,RIGHT(AO$3,4)&amp;", ","")&amp;IF($AP193=1,RIGHT(AP$3,4)&amp;", ","")&amp;IF($AQ193=1,RIGHT(AQ$3,4)&amp;", ","")&amp;IF($AR193=1,RIGHT(AR$3,4)&amp;", ","")&amp;IF($AS193=1,RIGHT(AS$3,4)&amp;", ","")</f>
-        <v xml:space="preserve">1985, 1986, 1987, 1988, 1989, 1990, 1991, 1992, 1993, 1994, 1995, 1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, </v>
+      <c r="AX193" s="2"/>
+      <c r="AY193" t="str">
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">1985, 1986, 1987, 1988, 1989, 1990, 1991, 1992, 1993, 1994, 1995, 1996, 1997, 1998, 1999, 2000, 2001, 2002, 2003, 2004, 2005, 2006, 2007, 2008, 2009, 2010, 2011, 2012, 2013, 2014, 2015, 2016, 2017, 2018, 2019, 2020, 2021, 2022, 2023, 2024, 2025, </v>
       </c>
     </row>
   </sheetData>
@@ -51263,64 +51473,67 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="AT153" r:id="rId1" xr:uid="{825CA162-48F0-45DA-9EE1-236C94FDF0C8}"/>
-    <hyperlink ref="AT151" r:id="rId2" xr:uid="{3E83B08B-A50F-4607-85F7-1534B161A3D6}"/>
-    <hyperlink ref="AU171" r:id="rId3" xr:uid="{7B6F629E-9908-4EEC-8BD1-7395AB48D6E2}"/>
-    <hyperlink ref="AU175" r:id="rId4" xr:uid="{70A78B0A-F50B-43B4-86FB-D1871B4DA162}"/>
-    <hyperlink ref="AU180" r:id="rId5" xr:uid="{13106DE9-76A4-40AA-87ED-A4521B291D91}"/>
-    <hyperlink ref="AV180" r:id="rId6" xr:uid="{4ACF1BB0-431E-48B4-9CD4-0CCCF940D3A1}"/>
-    <hyperlink ref="AT185" r:id="rId7" location="id=gecon-gezondheidsenquete-2019-0" xr:uid="{32716EEE-CC48-4816-94E7-B8CC9CAEE0D2}"/>
-    <hyperlink ref="AU163" r:id="rId8" xr:uid="{9F83ADE9-1786-4E0C-89C9-03A6232F153F}"/>
-    <hyperlink ref="AT178" r:id="rId9" xr:uid="{443A7F28-1BD9-449E-8FC9-871D8FFE07A1}"/>
-    <hyperlink ref="AT175" r:id="rId10" xr:uid="{9DA74F05-2AA2-4C1B-8415-FE511E9B33D4}"/>
-    <hyperlink ref="AT152" r:id="rId11" xr:uid="{6B58DD49-EE68-4427-8376-50F57EC3B560}"/>
-    <hyperlink ref="AT157" r:id="rId12" xr:uid="{4CC94269-80CB-4372-B4ED-A702134D66C7}"/>
-    <hyperlink ref="AT158" r:id="rId13" display="https://slovak.statistics.sk/wps/portal/ext/themes/demography/health/about/!ut/p/z1/pZNNc4IwEIZ_iweOJRsSQ-wt2Bqxjgqotbl00KHIjICDtLT_vtiPA1pDO92cMnnedzebDVJohVQWviRxWCZ5Fu7q_YNij57tcsfBAriztMC1Jz6-8zyJfYruT4CJfwvuXMykP6IYaBepxnHXBnAnwQJgGUAwZV_6vhRDao8B-Fh2wRXDhd_zCAFBTvQX8sOFEPA7vaZATf1iSPT6I6DTz1lLfvY__RH44_3PAKVvbxBltYf6wHSv2OajtIMicQsA3w6DYGaJHpX9G386qCexb_FgzCyANgdGzoBmLxy7JYVkaIRUsk7NapOaYFqU9oBxDJhzsGxy_EwiWxMeI1VET1ERFeZzUf-xbVnuD9cGGFBVlRnnebyLzE2eGvCTZJsfSrRqkmifLj5j9eom9bpS67dKdDrvzj5Ymw!!/dz/d5/L2dBISEvZ0FBIS9nQSEh/" xr:uid="{F88A2D5E-750E-42F8-818C-A3DFF546ADC5}"/>
-    <hyperlink ref="AT161" r:id="rId14" display="https://www.abs.gov.au/AUSSTATS/abs@.nsf/second+level+view?ReadForm&amp;prodno=4324.0.55.001&amp;viewtitle=Microdata:%20Australian%20Health%20Survey,%20National%20Health%20Survey~2011-12~Previous~24/09/2013&amp;&amp;tabname=Past%20Future%20Issues&amp;prodno=4324.0.55.001&amp;issue=2011-12&amp;num=&amp;view=&amp;" xr:uid="{D05E16EC-5ED5-4AD2-B807-4A5D61B1124A}"/>
-    <hyperlink ref="AT162" r:id="rId15" xr:uid="{E9AEE40B-4598-4F8B-9FDE-3431A25BD9F6}"/>
-    <hyperlink ref="AT163" r:id="rId16" xr:uid="{F5A347F9-5612-4E0A-9409-DFB95428D655}"/>
-    <hyperlink ref="AT166" r:id="rId17" xr:uid="{AA7D3175-1E61-4BBE-AD5E-FFD8F237C059}"/>
-    <hyperlink ref="AT167" r:id="rId18" xr:uid="{CBCE1D2C-4A74-4928-8910-017533353E10}"/>
-    <hyperlink ref="AT168" r:id="rId19" xr:uid="{1BE7066E-E732-4177-B882-1FF3DFBAA709}"/>
-    <hyperlink ref="AT171" r:id="rId20" xr:uid="{AA8A5E9E-37D2-4994-B5F3-53FC4DB497A4}"/>
-    <hyperlink ref="AT173" r:id="rId21" xr:uid="{DC2F19CA-F606-4CB4-9ED8-9BF6E7096E2E}"/>
-    <hyperlink ref="AT176" r:id="rId22" xr:uid="{ECD27DB7-553D-4295-96FB-85289FC471E5}"/>
-    <hyperlink ref="AT177" r:id="rId23" xr:uid="{88745DB7-47F6-459C-9787-E0A5695EFFE7}"/>
-    <hyperlink ref="AT179" r:id="rId24" xr:uid="{DE49FFE8-33F1-4ECC-BFF2-18BFBCACF622}"/>
-    <hyperlink ref="AU179" r:id="rId25" xr:uid="{13C2927D-B4AD-4B53-9760-B190B78B3B88}"/>
-    <hyperlink ref="AT180" r:id="rId26" xr:uid="{7730883F-4551-47BA-8B3C-316195863537}"/>
-    <hyperlink ref="AT181" r:id="rId27" location="SelectStatsBoxDiv" xr:uid="{1255FDA6-5929-4B0A-A990-FF1A4DADFFCF}"/>
-    <hyperlink ref="AV181" r:id="rId28" xr:uid="{EE6F20C0-9207-4E3A-A8AD-08C41D2ECE28}"/>
-    <hyperlink ref="AT183" r:id="rId29" xr:uid="{97150B88-470C-4CF1-ADD9-DE04C0B6318C}"/>
-    <hyperlink ref="AT186" r:id="rId30" xr:uid="{1CFCC8E2-8986-448B-A1E9-2E0B63B06790}"/>
-    <hyperlink ref="AU186" r:id="rId31" xr:uid="{23FDB280-0804-4C2C-B4D0-6B2B170FB7B0}"/>
-    <hyperlink ref="AT188" r:id="rId32" xr:uid="{C213892E-7963-413C-B9F7-B67E8FCE458D}"/>
-    <hyperlink ref="AU188" r:id="rId33" xr:uid="{19BA76C8-E1FB-4AEF-AD22-4C7938CAF48C}"/>
-    <hyperlink ref="AT193" r:id="rId34" xr:uid="{3C8BDB83-7A2A-4A81-A692-37CB3F7DF77A}"/>
-    <hyperlink ref="AT174" r:id="rId35" xr:uid="{C2E8F023-E46A-4B93-AE3B-C0B05B23CA48}"/>
-    <hyperlink ref="AW178" r:id="rId36" xr:uid="{A8C5223F-674E-49F9-B4B0-37C0913D8E92}"/>
-    <hyperlink ref="AU151" r:id="rId37" xr:uid="{6C1ED42E-3ECF-4A90-A254-4E557A8192FC}"/>
-    <hyperlink ref="AT154" r:id="rId38" xr:uid="{FF14B80F-BC20-47AF-8A23-84BB8C09A5B7}"/>
-    <hyperlink ref="AT169" r:id="rId39" xr:uid="{DA4D46F1-1AEA-4993-9B4F-49E862D375C5}"/>
-    <hyperlink ref="AT170" r:id="rId40" xr:uid="{5851511B-3347-4BF7-B3BD-40109B413330}"/>
-    <hyperlink ref="AT172" r:id="rId41" location="Kuidas-andmeid-kogutakse-114" xr:uid="{2AB22F7E-1C54-4384-A771-BD87001D2238}"/>
-    <hyperlink ref="AU174" r:id="rId42" xr:uid="{82D95A07-205F-467C-9BB9-740168B3682D}"/>
-    <hyperlink ref="AW180" r:id="rId43" xr:uid="{6B0864A8-B5C4-48C7-AE3C-807A57DEB746}"/>
-    <hyperlink ref="AT191" r:id="rId44" xr:uid="{E0366D4D-967C-4EDA-BD94-5EEB4D1E26BF}"/>
-    <hyperlink ref="AT192" r:id="rId45" xr:uid="{1C0A9137-495B-4875-950F-FFFAA5109F7A}"/>
-    <hyperlink ref="AU193" r:id="rId46" xr:uid="{59A61076-33A5-403B-B4A7-AABAA0C41A21}"/>
+    <hyperlink ref="AU153" r:id="rId1" xr:uid="{825CA162-48F0-45DA-9EE1-236C94FDF0C8}"/>
+    <hyperlink ref="AU151" r:id="rId2" xr:uid="{3E83B08B-A50F-4607-85F7-1534B161A3D6}"/>
+    <hyperlink ref="AV171" r:id="rId3" xr:uid="{7B6F629E-9908-4EEC-8BD1-7395AB48D6E2}"/>
+    <hyperlink ref="AV175" r:id="rId4" xr:uid="{70A78B0A-F50B-43B4-86FB-D1871B4DA162}"/>
+    <hyperlink ref="AV180" r:id="rId5" xr:uid="{13106DE9-76A4-40AA-87ED-A4521B291D91}"/>
+    <hyperlink ref="AW180" r:id="rId6" xr:uid="{4ACF1BB0-431E-48B4-9CD4-0CCCF940D3A1}"/>
+    <hyperlink ref="AU185" r:id="rId7" location="id=gecon-gezondheidsenquete-2019-0" xr:uid="{32716EEE-CC48-4816-94E7-B8CC9CAEE0D2}"/>
+    <hyperlink ref="AV163" r:id="rId8" xr:uid="{9F83ADE9-1786-4E0C-89C9-03A6232F153F}"/>
+    <hyperlink ref="AU178" r:id="rId9" xr:uid="{443A7F28-1BD9-449E-8FC9-871D8FFE07A1}"/>
+    <hyperlink ref="AU175" r:id="rId10" xr:uid="{9DA74F05-2AA2-4C1B-8415-FE511E9B33D4}"/>
+    <hyperlink ref="AU152" r:id="rId11" xr:uid="{6B58DD49-EE68-4427-8376-50F57EC3B560}"/>
+    <hyperlink ref="AU157" r:id="rId12" xr:uid="{4CC94269-80CB-4372-B4ED-A702134D66C7}"/>
+    <hyperlink ref="AU158" r:id="rId13" display="https://slovak.statistics.sk/wps/portal/ext/themes/demography/health/about/!ut/p/z1/pZNNc4IwEIZ_iweOJRsSQ-wt2Bqxjgqotbl00KHIjICDtLT_vtiPA1pDO92cMnnedzebDVJohVQWviRxWCZ5Fu7q_YNij57tcsfBAriztMC1Jz6-8zyJfYruT4CJfwvuXMykP6IYaBepxnHXBnAnwQJgGUAwZV_6vhRDao8B-Fh2wRXDhd_zCAFBTvQX8sOFEPA7vaZATf1iSPT6I6DTz1lLfvY__RH44_3PAKVvbxBltYf6wHSv2OajtIMicQsA3w6DYGaJHpX9G386qCexb_FgzCyANgdGzoBmLxy7JYVkaIRUsk7NapOaYFqU9oBxDJhzsGxy_EwiWxMeI1VET1ERFeZzUf-xbVnuD9cGGFBVlRnnebyLzE2eGvCTZJsfSrRqkmifLj5j9eom9bpS67dKdDrvzj5Ymw!!/dz/d5/L2dBISEvZ0FBIS9nQSEh/" xr:uid="{F88A2D5E-750E-42F8-818C-A3DFF546ADC5}"/>
+    <hyperlink ref="AU161" r:id="rId14" display="https://www.abs.gov.au/AUSSTATS/abs@.nsf/second+level+view?ReadForm&amp;prodno=4324.0.55.001&amp;viewtitle=Microdata:%20Australian%20Health%20Survey,%20National%20Health%20Survey~2011-12~Previous~24/09/2013&amp;&amp;tabname=Past%20Future%20Issues&amp;prodno=4324.0.55.001&amp;issue=2011-12&amp;num=&amp;view=&amp;" xr:uid="{D05E16EC-5ED5-4AD2-B807-4A5D61B1124A}"/>
+    <hyperlink ref="AU162" r:id="rId15" xr:uid="{E9AEE40B-4598-4F8B-9FDE-3431A25BD9F6}"/>
+    <hyperlink ref="AU163" r:id="rId16" xr:uid="{F5A347F9-5612-4E0A-9409-DFB95428D655}"/>
+    <hyperlink ref="AU166" r:id="rId17" xr:uid="{AA7D3175-1E61-4BBE-AD5E-FFD8F237C059}"/>
+    <hyperlink ref="AU167" r:id="rId18" xr:uid="{CBCE1D2C-4A74-4928-8910-017533353E10}"/>
+    <hyperlink ref="AU168" r:id="rId19" xr:uid="{1BE7066E-E732-4177-B882-1FF3DFBAA709}"/>
+    <hyperlink ref="AU171" r:id="rId20" xr:uid="{AA8A5E9E-37D2-4994-B5F3-53FC4DB497A4}"/>
+    <hyperlink ref="AU173" r:id="rId21" xr:uid="{DC2F19CA-F606-4CB4-9ED8-9BF6E7096E2E}"/>
+    <hyperlink ref="AU176" r:id="rId22" xr:uid="{ECD27DB7-553D-4295-96FB-85289FC471E5}"/>
+    <hyperlink ref="AU177" r:id="rId23" xr:uid="{88745DB7-47F6-459C-9787-E0A5695EFFE7}"/>
+    <hyperlink ref="AU179" r:id="rId24" xr:uid="{DE49FFE8-33F1-4ECC-BFF2-18BFBCACF622}"/>
+    <hyperlink ref="AV179" r:id="rId25" xr:uid="{13C2927D-B4AD-4B53-9760-B190B78B3B88}"/>
+    <hyperlink ref="AU180" r:id="rId26" xr:uid="{7730883F-4551-47BA-8B3C-316195863537}"/>
+    <hyperlink ref="AU181" r:id="rId27" location="SelectStatsBoxDiv" xr:uid="{1255FDA6-5929-4B0A-A990-FF1A4DADFFCF}"/>
+    <hyperlink ref="AW181" r:id="rId28" xr:uid="{EE6F20C0-9207-4E3A-A8AD-08C41D2ECE28}"/>
+    <hyperlink ref="AU183" r:id="rId29" xr:uid="{97150B88-470C-4CF1-ADD9-DE04C0B6318C}"/>
+    <hyperlink ref="AU186" r:id="rId30" xr:uid="{1CFCC8E2-8986-448B-A1E9-2E0B63B06790}"/>
+    <hyperlink ref="AV186" r:id="rId31" xr:uid="{23FDB280-0804-4C2C-B4D0-6B2B170FB7B0}"/>
+    <hyperlink ref="AU188" r:id="rId32" xr:uid="{C213892E-7963-413C-B9F7-B67E8FCE458D}"/>
+    <hyperlink ref="AV188" r:id="rId33" xr:uid="{19BA76C8-E1FB-4AEF-AD22-4C7938CAF48C}"/>
+    <hyperlink ref="AU193" r:id="rId34" xr:uid="{3C8BDB83-7A2A-4A81-A692-37CB3F7DF77A}"/>
+    <hyperlink ref="AU174" r:id="rId35" xr:uid="{C2E8F023-E46A-4B93-AE3B-C0B05B23CA48}"/>
+    <hyperlink ref="AX178" r:id="rId36" xr:uid="{A8C5223F-674E-49F9-B4B0-37C0913D8E92}"/>
+    <hyperlink ref="AV151" r:id="rId37" xr:uid="{6C1ED42E-3ECF-4A90-A254-4E557A8192FC}"/>
+    <hyperlink ref="AU154" r:id="rId38" xr:uid="{FF14B80F-BC20-47AF-8A23-84BB8C09A5B7}"/>
+    <hyperlink ref="AU169" r:id="rId39" xr:uid="{DA4D46F1-1AEA-4993-9B4F-49E862D375C5}"/>
+    <hyperlink ref="AU170" r:id="rId40" xr:uid="{5851511B-3347-4BF7-B3BD-40109B413330}"/>
+    <hyperlink ref="AU172" r:id="rId41" location="Kuidas-andmeid-kogutakse-114" xr:uid="{2AB22F7E-1C54-4384-A771-BD87001D2238}"/>
+    <hyperlink ref="AV174" r:id="rId42" xr:uid="{82D95A07-205F-467C-9BB9-740168B3682D}"/>
+    <hyperlink ref="AX180" r:id="rId43" xr:uid="{6B0864A8-B5C4-48C7-AE3C-807A57DEB746}"/>
+    <hyperlink ref="AU191" r:id="rId44" xr:uid="{E0366D4D-967C-4EDA-BD94-5EEB4D1E26BF}"/>
+    <hyperlink ref="AU192" r:id="rId45" xr:uid="{1C0A9137-495B-4875-950F-FFFAA5109F7A}"/>
+    <hyperlink ref="AV193" r:id="rId46" xr:uid="{59A61076-33A5-403B-B4A7-AABAA0C41A21}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId47"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:W151"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.33203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>18</v>
       </c>
@@ -51370,7 +51583,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -51422,7 +51635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -51474,7 +51687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -51526,7 +51739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -51578,7 +51791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -51636,7 +51849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -51694,7 +51907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -51752,7 +51965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -51810,7 +52023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>49</v>
       </c>
@@ -51868,7 +52081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>50</v>
       </c>
@@ -51926,7 +52139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -51984,7 +52197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -52036,7 +52249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -52094,7 +52307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -52152,7 +52365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -52210,7 +52423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>56</v>
       </c>
@@ -52268,7 +52481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>57</v>
       </c>
@@ -52320,7 +52533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>58</v>
       </c>
@@ -52372,7 +52585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>59</v>
       </c>
@@ -52424,7 +52637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -52482,7 +52695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>61</v>
       </c>
@@ -52540,7 +52753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -52592,7 +52805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -52650,7 +52863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -52708,7 +52921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -52760,7 +52973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -52818,7 +53031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>68</v>
       </c>
@@ -52870,7 +53083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>69</v>
       </c>
@@ -52922,7 +53135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>70</v>
       </c>
@@ -52974,7 +53187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>71</v>
       </c>
@@ -53032,7 +53245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -53084,7 +53297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>73</v>
       </c>
@@ -53142,7 +53355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>74</v>
       </c>
@@ -53200,7 +53413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>75</v>
       </c>
@@ -53258,7 +53471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>76</v>
       </c>
@@ -53310,7 +53523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>77</v>
       </c>
@@ -53362,7 +53575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>209</v>
       </c>
@@ -53414,7 +53627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -53466,7 +53679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -53518,7 +53731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -53570,7 +53783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>81</v>
       </c>
@@ -53622,7 +53835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -53680,7 +53893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>83</v>
       </c>
@@ -53738,7 +53951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -53796,7 +54009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -53854,7 +54067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>86</v>
       </c>
@@ -53912,7 +54125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -53964,7 +54177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>88</v>
       </c>
@@ -54016,7 +54229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>89</v>
       </c>
@@ -54074,7 +54287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>90</v>
       </c>
@@ -54132,7 +54345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>91</v>
       </c>
@@ -54190,7 +54403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>92</v>
       </c>
@@ -54242,7 +54455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>93</v>
       </c>
@@ -54294,7 +54507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>190</v>
       </c>
@@ -54346,7 +54559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>94</v>
       </c>
@@ -54404,7 +54617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:23">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>95</v>
       </c>
@@ -54456,7 +54669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>96</v>
       </c>
@@ -54508,7 +54721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>97</v>
       </c>
@@ -54566,7 +54779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>98</v>
       </c>
@@ -54624,7 +54837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>99</v>
       </c>
@@ -54676,7 +54889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:23">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>100</v>
       </c>
@@ -54734,7 +54947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:23">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>101</v>
       </c>
@@ -54786,7 +54999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>102</v>
       </c>
@@ -54844,7 +55057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:23">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>103</v>
       </c>
@@ -54896,7 +55109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:23">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>104</v>
       </c>
@@ -54948,7 +55161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:23">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>105</v>
       </c>
@@ -55000,7 +55213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:23">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>493</v>
       </c>
@@ -55043,7 +55256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:23">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>106</v>
       </c>
@@ -55101,7 +55314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:23">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>107</v>
       </c>
@@ -55159,7 +55372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:23">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>108</v>
       </c>
@@ -55217,7 +55430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:23">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>109</v>
       </c>
@@ -55269,7 +55482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:23">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -55321,7 +55534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:23">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>111</v>
       </c>
@@ -55379,7 +55592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:23">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>112</v>
       </c>
@@ -55431,7 +55644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:23">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>192</v>
       </c>
@@ -55483,7 +55696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:23">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>191</v>
       </c>
@@ -55535,7 +55748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:23">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>113</v>
       </c>
@@ -55593,7 +55806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:23">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>114</v>
       </c>
@@ -55645,7 +55858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:23">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>115</v>
       </c>
@@ -55697,7 +55910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:23">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>116</v>
       </c>
@@ -55749,7 +55962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:23">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>117</v>
       </c>
@@ -55801,7 +56014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:23">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>118</v>
       </c>
@@ -55859,7 +56072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:23">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>119</v>
       </c>
@@ -55911,7 +56124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:23">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>120</v>
       </c>
@@ -55969,7 +56182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:23">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>121</v>
       </c>
@@ -56021,7 +56234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:23">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>122</v>
       </c>
@@ -56079,7 +56292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:23">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>123</v>
       </c>
@@ -56131,7 +56344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:23">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>124</v>
       </c>
@@ -56183,7 +56396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:23">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>125</v>
       </c>
@@ -56235,7 +56448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:23">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>126</v>
       </c>
@@ -56293,7 +56506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:23">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>127</v>
       </c>
@@ -56351,7 +56564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:23">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>128</v>
       </c>
@@ -56403,7 +56616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:23">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>129</v>
       </c>
@@ -56461,7 +56674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:23">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>130</v>
       </c>
@@ -56519,7 +56732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:23">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>131</v>
       </c>
@@ -56577,7 +56790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:23">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>132</v>
       </c>
@@ -56635,7 +56848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:23">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>133</v>
       </c>
@@ -56693,7 +56906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:23">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>135</v>
       </c>
@@ -56751,7 +56964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:23">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>136</v>
       </c>
@@ -56809,7 +57022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:23">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>137</v>
       </c>
@@ -56867,7 +57080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:23">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>138</v>
       </c>
@@ -56919,7 +57132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:23">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>139</v>
       </c>
@@ -56971,7 +57184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:23">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>140</v>
       </c>
@@ -57029,7 +57242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:23">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>141</v>
       </c>
@@ -57081,7 +57294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:23">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>142</v>
       </c>
@@ -57139,7 +57352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:23">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>494</v>
       </c>
@@ -57191,7 +57404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:23">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>145</v>
       </c>
@@ -57243,7 +57456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:23">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>146</v>
       </c>
@@ -57295,7 +57508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:23">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>147</v>
       </c>
@@ -57353,7 +57566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:23">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>148</v>
       </c>
@@ -57405,7 +57618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:23">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>149</v>
       </c>
@@ -57463,7 +57676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:23">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>150</v>
       </c>
@@ -57515,7 +57728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:23">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>151</v>
       </c>
@@ -57573,7 +57786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:23">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>152</v>
       </c>
@@ -57631,7 +57844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:23">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>153</v>
       </c>
@@ -57683,7 +57896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:23">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>154</v>
       </c>
@@ -57726,7 +57939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:23">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>155</v>
       </c>
@@ -57784,7 +57997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:23">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>156</v>
       </c>
@@ -57842,7 +58055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:23">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>195</v>
       </c>
@@ -57894,7 +58107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:23">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>157</v>
       </c>
@@ -57952,7 +58165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:23">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>158</v>
       </c>
@@ -58004,7 +58217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:23">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>159</v>
       </c>
@@ -58062,7 +58275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:23">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>160</v>
       </c>
@@ -58114,7 +58327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:23">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>161</v>
       </c>
@@ -58172,7 +58385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:23">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>162</v>
       </c>
@@ -58224,7 +58437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:23">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -58276,7 +58489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:23">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>164</v>
       </c>
@@ -58334,7 +58547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:23">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>495</v>
       </c>
@@ -58386,7 +58599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:23">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>166</v>
       </c>
@@ -58438,7 +58651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:23">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>167</v>
       </c>
@@ -58496,7 +58709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:23">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>168</v>
       </c>
@@ -58554,7 +58767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:23">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>169</v>
       </c>
@@ -58606,7 +58819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:23">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>170</v>
       </c>
@@ -58646,7 +58859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:23">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>171</v>
       </c>
@@ -58698,7 +58911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:23">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>172</v>
       </c>
@@ -58756,7 +58969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:23">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>173</v>
       </c>
@@ -58808,7 +59021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:23">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>174</v>
       </c>
@@ -58866,7 +59079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:23">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>175</v>
       </c>
@@ -58924,7 +59137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:23">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>176</v>
       </c>
@@ -58976,7 +59189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:23">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>177</v>
       </c>
@@ -59034,7 +59247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:23">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>178</v>
       </c>
@@ -59092,7 +59305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:23">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>179</v>
       </c>
@@ -59144,7 +59357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:23">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>496</v>
       </c>
@@ -59187,7 +59400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:23">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>180</v>
       </c>
@@ -59239,7 +59452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:23">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>182</v>
       </c>
@@ -59297,7 +59510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:23">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>183</v>
       </c>
@@ -59349,7 +59562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:23">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>497</v>
       </c>
@@ -59407,7 +59620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:23">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>184</v>
       </c>
@@ -59465,7 +59678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:23">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>185</v>
       </c>
@@ -59525,11 +59738,34 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;R_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Official Use Only</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3e02667f-0271-471b-bd6e-11a2e16def1d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b19ad29f-88fa-4d62-ac16-34b992563bf9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ADB9CD767C4FF34281D6635032C5B89D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3b7ad1acb7d07f4c67b79ea712f2c443">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b19ad29f-88fa-4d62-ac16-34b992563bf9" xmlns:ns3="e781ea9d-1795-4792-8d8d-c86ae526af93" xmlns:ns4="3e02667f-0271-471b-bd6e-11a2e16def1d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e0bd56705adf4bb69ae57d53dbdc9cd2" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
@@ -59777,34 +60013,48 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3e02667f-0271-471b-bd6e-11a2e16def1d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b19ad29f-88fa-4d62-ac16-34b992563bf9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC6A35A2-240D-4BB0-84F0-593E5263A1AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5480555-FFD5-4FE0-A894-482D4B002F15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4ED005E-A32D-4A12-AB3F-2C25D7ACBB61}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4ED005E-A32D-4A12-AB3F-2C25D7ACBB61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3e02667f-0271-471b-bd6e-11a2e16def1d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e781ea9d-1795-4792-8d8d-c86ae526af93"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5480555-FFD5-4FE0-A894-482D4B002F15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC6A35A2-240D-4BB0-84F0-593E5263A1AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b19ad29f-88fa-4d62-ac16-34b992563bf9"/>
+    <ds:schemaRef ds:uri="e781ea9d-1795-4792-8d8d-c86ae526af93"/>
+    <ds:schemaRef ds:uri="3e02667f-0271-471b-bd6e-11a2e16def1d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>